--- a/08_Reports - Доклади - Berichte/Accounting_Cash_Flow/validation_results.xlsx
+++ b/08_Reports - Доклади - Berichte/Accounting_Cash_Flow/validation_results.xlsx
@@ -90,12 +90,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/03_Employee_Payslips/Entgeltbescheinigungen 06-2025.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/02_Payroll/312_neut__Verdienstbescheinigung_Brutto_Netto_01_08_2023_-_31_07_2024.pdf</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -105,37 +105,37 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>month; total_netto</t>
+          <t>month</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>{"month": "2000-01", "total_netto": "18.07"}</t>
+          <t>{"month": "2023-08"}</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>source filename month hint: 06-2025</t>
+          <t>sampled values are supported by source text/path</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>WRONG</t>
+          <t>CORRECT</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>supported fields: total_netto; unsupported fields: month</t>
+          <t>supported fields: month; unsupported fields: none</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>Month parser selected a nearby date or unrelated filename token.</t>
+          <t/>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>Prefer Leistungszeitraum/document period labels and filename month patterns over first date token.</t>
+          <t>No parser fix required for sampled row.</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -157,12 +157,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/04_Health_Insurance/04-2021 #9109.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/02_Payroll/Lohnauswertungen_Juli_2024.pdf</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -172,12 +172,12 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>month; total_netto</t>
+          <t>month</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>{"month": "2021-04", "total_netto": "12.03"}</t>
+          <t>{"month": "2024-07"}</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -192,7 +192,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>supported fields: month, total_netto; unsupported fields: none</t>
+          <t>supported fields: month; unsupported fields: none</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -224,12 +224,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>4</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/04_Health_Insurance/12-2021 #9109.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/02_Payroll/Lohnauswertungen_Juli_2025.pdf</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -239,12 +239,12 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>month; total_netto</t>
+          <t>month</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>{"month": "2021-12", "total_netto": "13.12"}</t>
+          <t>{"month": "2024-11"}</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -259,7 +259,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>supported fields: month, total_netto; unsupported fields: none</t>
+          <t>supported fields: month; unsupported fields: none</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -291,12 +291,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>5</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/06_Bank_Payments/20240123_60222_10160_Rechnung.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/02_Payroll/Lohnauswertungen_Juli_2025__copy2.pdf</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -306,12 +306,12 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>month; total_brutto; total_netto</t>
+          <t>month</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>{"month": "2024-01", "total_brutto": "517.65", "total_netto": "435.00"}</t>
+          <t>{"month": "2020-07"}</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -326,7 +326,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>supported fields: month, total_brutto, total_netto; unsupported fields: none</t>
+          <t>supported fields: month; unsupported fields: none</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -358,12 +358,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>6</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/08_Operating_Costs/40579 - Rechnung 240155_2024 vom 17.02.2024, Aufträge 31_23, 33_23, 34_23, Mandant 42303.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/02_Payroll/Lohnauswertungen_Mai_2024-1.pdf</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -373,37 +373,37 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>month; total_brutto; total_netto</t>
+          <t>month</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>{"month": "2024-02", "total_brutto": "10499.90", "total_netto": "10499.90"}</t>
+          <t>{"month": "2022-10"}</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>total_brutto: not found; total_netto: not found</t>
+          <t>sampled values are supported by source text/path</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>CORRECT</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>supported fields: month; unsupported fields: total_brutto, total_netto</t>
+          <t>supported fields: month; unsupported fields: none</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>Extracted value was not directly found in the readable source text.</t>
+          <t/>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>Add field-specific validation patterns and source text snippets for this document type.</t>
+          <t>No parser fix required for sampled row.</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -425,12 +425,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>7</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/08_Operating_Costs/43029 - Rechnung 240697_2024 vom 31.07.2024, Aufträge 21_23, 21_24, 31_22, 31_23, 31_24, 33_24, 34_24, Mandant 42303.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/02_Payroll/Lohnauswertungen_Mai_2024.pdf</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -440,12 +440,12 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>month; total_netto</t>
+          <t>month</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>{"month": "2024-07", "total_netto": "19.00"}</t>
+          <t>{"month": "2024-06"}</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -460,7 +460,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>supported fields: month, total_netto; unsupported fields: none</t>
+          <t>supported fields: month; unsupported fields: none</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -492,12 +492,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>8</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/08_Operating_Costs/45027 - Rechnung 241185_2024 vom 29.11.2024, Aufträge 31_24, 33_24, 34_24, Mandant 42303.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/02_Payroll/Lohnauswertungen_März_2025.pdf</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -507,12 +507,12 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>month; total_netto</t>
+          <t>month</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>{"month": "2024-11", "total_netto": "19.00"}</t>
+          <t>{"month": "2025-04"}</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -527,7 +527,7 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>supported fields: month, total_netto; unsupported fields: none</t>
+          <t>supported fields: month; unsupported fields: none</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -559,12 +559,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>9</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/08_Operating_Costs/46583 - Rechnung 250253_2025 vom 14.03.2025, Aufträge 31_25, 33_24, 34_24, 34_25, Mandant 42303.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/02_Payroll/Lohnauswertungen_November_2024-1.pdf</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -574,37 +574,37 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>month; total_brutto; total_netto</t>
+          <t>month</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>{"month": "2025-03", "total_brutto": "11062.00", "total_netto": "11062.00"}</t>
+          <t>{"month": "2024-12"}</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>total_brutto: not found; total_netto: not found</t>
+          <t>sampled values are supported by source text/path</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>CORRECT</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>supported fields: month; unsupported fields: total_brutto, total_netto</t>
+          <t>supported fields: month; unsupported fields: none</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>Extracted value was not directly found in the readable source text.</t>
+          <t/>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>Add field-specific validation patterns and source text snippets for this document type.</t>
+          <t>No parser fix required for sampled row.</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -626,12 +626,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>10</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/08_Operating_Costs/CarlundCarla_RG424005125.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/02_Payroll/Lohnauswertungen_November_2024.pdf</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -641,12 +641,12 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>month; total_netto</t>
+          <t>month</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>{"month": "2024-09", "total_netto": "179.83"}</t>
+          <t>{"month": "2024-12"}</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -661,7 +661,7 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>supported fields: month, total_netto; unsupported fields: none</t>
+          <t>supported fields: month; unsupported fields: none</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -693,12 +693,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>11</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/08_Operating_Costs/Rechnung 2794 Zahariev KFZ Miete.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/02_Payroll/Lohnauswertungen_Oktober_2024.pdf</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -708,12 +708,12 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>month; total_netto</t>
+          <t>month</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>{"month": "2025-06", "total_netto": "60.00"}</t>
+          <t>{"month": "2024-11"}</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -728,7 +728,7 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>supported fields: month, total_netto; unsupported fields: none</t>
+          <t>supported fields: month; unsupported fields: none</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -755,17 +755,17 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Payroll</t>
+          <t>Health Insurance</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>5</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/08_Operating_Costs/Rechnung 2810 Zahariev TF Touren.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/02_Payroll/10001_03-2024_DivAuswertungen_DivMitarbeiter_8Z1.pdf</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -775,37 +775,37 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>month; total_netto</t>
+          <t>insurance_name</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>{"month": "2025-07", "total_netto": "7980.00"}</t>
+          <t>{"insurance_name": "AOK Plus"}</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>total_netto: not found</t>
+          <t>sampled values are supported by source text/path</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>CORRECT</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>supported fields: month; unsupported fields: total_netto</t>
+          <t>supported fields: insurance_name; unsupported fields: none</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>Extracted value was not directly found in the readable source text.</t>
+          <t/>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>Add field-specific validation patterns and source text snippets for this document type.</t>
+          <t>No parser fix required for sampled row.</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -822,17 +822,17 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Payroll</t>
+          <t>Health Insurance</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>58</t>
+          <t>7</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/08_Operating_Costs/Unternehmerabrechnung - VP 120-2400000826.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/02_Payroll/10001_04-2024_DivAuswertungen_DivMitarbeiter_BZ1.pdf</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -842,37 +842,37 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>month; total_netto</t>
+          <t>insurance_name; amount_paid</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>{"month": "2024-01", "total_netto": "100833.17"}</t>
+          <t>{"insurance_name": "AOK Plus", "amount_paid": "1548.00"}</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>total_netto: not found</t>
+          <t>sampled values are supported by source text/path</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>CORRECT</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>supported fields: month; unsupported fields: total_netto</t>
+          <t>supported fields: insurance_name, amount_paid; unsupported fields: none</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>Extracted value was not directly found in the readable source text.</t>
+          <t/>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>Add field-specific validation patterns and source text snippets for this document type.</t>
+          <t>No parser fix required for sampled row.</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -889,17 +889,17 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Payroll</t>
+          <t>Health Insurance</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>64</t>
+          <t>9</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/08_Operating_Costs/Unternehmerabrechnung - VP 120-2400035649.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/02_Payroll/10001_06-2024_DivAuswertungen_DivMitarbeiter_HZ1.pdf</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -909,12 +909,12 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>month; total_netto</t>
+          <t>insurance_name; amount_paid</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>{"month": "2024-01", "total_netto": "511.46"}</t>
+          <t>{"insurance_name": "AOK Plus", "amount_paid": "1806.00"}</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -929,7 +929,7 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>supported fields: month, total_netto; unsupported fields: none</t>
+          <t>supported fields: insurance_name, amount_paid; unsupported fields: none</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -956,17 +956,17 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Payroll</t>
+          <t>Health Insurance</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>14</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/09_Enrico_Forwarded/Docutain Dokument.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/02_Payroll/10001_09-2024_Brutto_NettoProbe_00051_QZ1.pdf</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -976,12 +976,12 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>month; total_netto</t>
+          <t>insurance_name</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>{"month": "2024-07", "total_netto": "2.06"}</t>
+          <t>{"insurance_name": "TK"}</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -991,22 +991,22 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>WRONG</t>
+          <t>CORRECT</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>supported fields: total_netto; unsupported fields: month</t>
+          <t>supported fields: insurance_name; unsupported fields: none</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>Month parser selected a nearby date or unrelated filename token.</t>
+          <t/>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>Prefer Leistungszeitraum/document period labels and filename month patterns over first date token.</t>
+          <t>No parser fix required for sampled row.</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -1023,17 +1023,17 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Payroll</t>
+          <t>Health Insurance</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>17</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/09_Enrico_Forwarded/gutschrift April 2025 zahariev.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/02_Payroll/10001_12-2023_Brutto_NettoProbe_00025_ZZ1.pdf</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -1043,37 +1043,37 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>month; total_netto</t>
+          <t>insurance_name; amount_paid</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>{"month": "2025-04", "total_netto": "152766.69"}</t>
+          <t>{"insurance_name": "TK", "amount_paid": "2619.35"}</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>total_netto: not found</t>
+          <t>sampled values are supported by source text/path</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>CORRECT</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>supported fields: month; unsupported fields: total_netto</t>
+          <t>supported fields: insurance_name, amount_paid; unsupported fields: none</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>Extracted value was not directly found in the readable source text.</t>
+          <t/>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>Add field-specific validation patterns and source text snippets for this document type.</t>
+          <t>No parser fix required for sampled row.</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -1090,17 +1090,17 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Payroll</t>
+          <t>Health Insurance</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>26</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/09_Enrico_Forwarded/Gutschrift Zahariev 74 30.06.2025.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/02_Payroll/Lohnauswertungen_März_2025.pdf</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -1110,37 +1110,37 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>month; total_netto</t>
+          <t>month; insurance_name</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>{"month": "2025-06", "total_netto": "46548.70"}</t>
+          <t>{"month": "2025-04", "insurance_name": "AOK Plus"}</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>total_netto: not found</t>
+          <t>sampled values are supported by source text/path</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>CORRECT</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>supported fields: month; unsupported fields: total_netto</t>
+          <t>supported fields: month, insurance_name; unsupported fields: none</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>Extracted value was not directly found in the readable source text.</t>
+          <t/>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>Add field-specific validation patterns and source text snippets for this document type.</t>
+          <t>No parser fix required for sampled row.</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -1157,17 +1157,17 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Payroll</t>
+          <t>Health Insurance</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>30</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/09_Enrico_Forwarded/Rechnung 2014 vom 05.12.2024 Sendungsverlust Zahariev.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/04_Health_Insurance/02-2022 #9109.pdf</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -1177,37 +1177,37 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>month; total_netto</t>
+          <t>month; insurance_name; amount_due; amount_paid</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>{"month": "2024-12", "total_netto": "10390.09"}</t>
+          <t>{"month": "2022-02", "insurance_name": "AOK Plus", "amount_due": "-949.37", "amount_paid": "952.60"}</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>total_netto: not found</t>
+          <t>sampled values are supported by source text/path</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>CORRECT</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>supported fields: month; unsupported fields: total_netto</t>
+          <t>supported fields: month, insurance_name, amount_due, amount_paid; unsupported fields: none</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>Extracted value was not directly found in the readable source text.</t>
+          <t/>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>Add field-specific validation patterns and source text snippets for this document type.</t>
+          <t>No parser fix required for sampled row.</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
@@ -1224,17 +1224,17 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Payroll</t>
+          <t>Health Insurance</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>92</t>
+          <t>32</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/09_Enrico_Forwarded/Rechnung 2023 vom 07.12.2024  Zahariev HERMES Bekleidung.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/04_Health_Insurance/04-2021 #9109.pdf</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -1244,12 +1244,12 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>month; total_netto</t>
+          <t>month; insurance_name; amount_paid</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>{"month": "2024-12", "total_netto": "42.43"}</t>
+          <t>{"month": "2021-04", "insurance_name": "AOK Plus", "amount_paid": "-775.00"}</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>supported fields: month, total_netto; unsupported fields: none</t>
+          <t>supported fields: month, insurance_name, amount_paid; unsupported fields: none</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -1291,17 +1291,17 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Payroll</t>
+          <t>Health Insurance</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>95</t>
+          <t>35</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/09_Enrico_Forwarded/Rechnung 2767 Zahariev Hermes Bearbeitungsgebuhr.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/04_Health_Insurance/06-2022 #9109.pdf</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -1311,12 +1311,12 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>month; total_netto</t>
+          <t>month; insurance_name; amount_due; amount_paid; unpaid_balance</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>{"month": "2025-04", "total_netto": "42.50"}</t>
+          <t>{"month": "2022-06", "insurance_name": "AOK Plus", "amount_due": "-935.88", "amount_paid": "-100.00", "unpaid_balance": "-30.30"}</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -1331,7 +1331,7 @@
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>supported fields: month, total_netto; unsupported fields: none</t>
+          <t>supported fields: month, insurance_name, amount_due, amount_paid, unpaid_balance; unsupported fields: none</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -1358,17 +1358,17 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Payroll</t>
+          <t>Health Insurance</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>96</t>
+          <t>37</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/11_Contribution_Lists/RE-53380_2024 13.08.2024 09_17_16.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/04_Health_Insurance/07-2022 #9109.pdf</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -1378,12 +1378,12 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>month; total_netto</t>
+          <t>month; insurance_name; amount_due; amount_paid; unpaid_balance</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>{"month": "2024-08", "total_netto": "0.00"}</t>
+          <t>{"month": "2022-07", "insurance_name": "AOK Plus", "amount_due": "-1030.32", "amount_paid": "-2750.24", "unpaid_balance": "19.08"}</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -1398,7 +1398,7 @@
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>supported fields: month, total_netto; unsupported fields: none</t>
+          <t>supported fields: month, insurance_name, amount_due, amount_paid, unpaid_balance; unsupported fields: none</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -1430,12 +1430,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>39</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/02_Payroll/10001_06-2024_DivAuswertungen_DivMitarbeiter_HZ1.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/04_Health_Insurance/10-2022 #9109.pdf</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1445,37 +1445,37 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>month; insurance_name; amount_due; amount_paid</t>
+          <t>month; insurance_name; amount_due; amount_paid; unpaid_balance</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>{"month": "2024-12", "insurance_name": "AOK Plus", "amount_due": "1118.00", "amount_paid": "1806.00"}</t>
+          <t>{"month": "2022-10", "insurance_name": "AOK Plus", "amount_due": "-983.10", "amount_paid": "-600.00", "unpaid_balance": "30.09"}</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>amount_due: not found; amount_paid: not found</t>
+          <t>sampled values are supported by source text/path</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>WRONG</t>
+          <t>CORRECT</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>supported fields: insurance_name; unsupported fields: month, amount_due, amount_paid</t>
+          <t>supported fields: month, insurance_name, amount_due, amount_paid, unpaid_balance; unsupported fields: none</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>Month parser selected a nearby date or unrelated filename token.</t>
+          <t/>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>Prefer Leistungszeitraum/document period labels and filename month patterns over first date token.</t>
+          <t>No parser fix required for sampled row.</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
@@ -1497,12 +1497,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>50</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/02_Payroll/10001_08-2024_Brutto_NettoProbe_00074_NZ1.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/04_Health_Insurance/Contributions 03.03.2025.docx</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1512,42 +1512,42 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>month; insurance_name; amount_paid</t>
+          <t>month; insurance_name</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>{"month": "2024-01", "insurance_name": "TK", "amount_paid": "1664.52"}</t>
+          <t>{"month": "2025-03", "insurance_name": "AOK Plus"}</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>amount_paid: not found</t>
+          <t>sampled values are supported by source text/path</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>WRONG</t>
+          <t>CORRECT</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>supported fields: insurance_name; unsupported fields: month, amount_paid</t>
+          <t>supported fields: month, insurance_name; unsupported fields: none</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>Month parser selected a nearby date or unrelated filename token.</t>
+          <t/>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>Prefer Leistungszeitraum/document period labels and filename month patterns over first date token.</t>
+          <t>No parser fix required for sampled row.</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>source read method: fitz</t>
+          <t>source read method: docx_xml</t>
         </is>
       </c>
     </row>
@@ -1564,12 +1564,12 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>52</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/02_Payroll/10001_09-2024_Brutto_NettoProbe_00051_QZ1.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/04_Health_Insurance/Contributions 13.03.2025.docx</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -1584,7 +1584,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>{"month": "2024-01", "insurance_name": "TK"}</t>
+          <t>{"month": "2025-03", "insurance_name": "AOK Plus"}</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -1594,27 +1594,27 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>WRONG</t>
+          <t>CORRECT</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>supported fields: insurance_name; unsupported fields: month</t>
+          <t>supported fields: month, insurance_name; unsupported fields: none</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>Month parser selected a nearby date or unrelated filename token.</t>
+          <t/>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>Prefer Leistungszeitraum/document period labels and filename month patterns over first date token.</t>
+          <t>No parser fix required for sampled row.</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>source read method: fitz</t>
+          <t>source read method: docx_xml</t>
         </is>
       </c>
     </row>
@@ -1631,12 +1631,12 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>54</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/02_Payroll/10001_12-2023_Brutto_NettoProbe_00025_ZZ1.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/04_Health_Insurance/Contributions.docx</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -1646,42 +1646,42 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>month; insurance_name; amount_paid</t>
+          <t>insurance_name</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>{"month": "2023-12", "insurance_name": "TK", "amount_paid": "2619.35"}</t>
+          <t>{"insurance_name": "AOK Plus"}</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>amount_paid: not found</t>
+          <t>sampled values are supported by source text/path</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>CORRECT</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>supported fields: month, insurance_name; unsupported fields: amount_paid</t>
+          <t>supported fields: insurance_name; unsupported fields: none</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>Extracted value was not directly found in the readable source text.</t>
+          <t/>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>Add field-specific validation patterns and source text snippets for this document type.</t>
+          <t>No parser fix required for sampled row.</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>source read method: fitz</t>
+          <t>source read method: docx_xml</t>
         </is>
       </c>
     </row>
@@ -1698,12 +1698,12 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>58</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/02_Payroll/Lohnauswertungen_November_2024-1.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/04_Health_Insurance/Sozialversicherungsanmeldungen.pdf</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -1713,12 +1713,12 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>month; insurance_name</t>
+          <t>insurance_name</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>{"month": "2024-12", "insurance_name": "KKH"}</t>
+          <t>{"insurance_name": "AOK"}</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -1733,7 +1733,7 @@
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>supported fields: month, insurance_name; unsupported fields: none</t>
+          <t>supported fields: insurance_name; unsupported fields: none</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
@@ -1748,7 +1748,7 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>source read method: fitz</t>
+          <t>source read method: recovered_text</t>
         </is>
       </c>
     </row>
@@ -1765,12 +1765,12 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>64</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/03_Employee_Payslips/Entgeltbescheinigungen 04-2025.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/05_Taxes/Test Pay ROll.pdf</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -1780,37 +1780,37 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>month; insurance_name; amount_due; amount_paid; due_date</t>
+          <t>insurance_name; amount_paid</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>{"month": "2003-01", "insurance_name": "AOK Plus", "amount_due": "28.04", "amount_paid": "4518.02", "due_date": "28.04.2025"}</t>
+          <t>{"insurance_name": "AOK Plus", "amount_paid": "1548.00"}</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>source filename month hint: 04-2025; amount_paid: not found</t>
+          <t>sampled values are supported by source text/path</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>WRONG</t>
+          <t>CORRECT</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>supported fields: insurance_name, amount_due, due_date; unsupported fields: month, amount_paid</t>
+          <t>supported fields: insurance_name, amount_paid; unsupported fields: none</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>Month parser selected a nearby date or unrelated filename token.</t>
+          <t/>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>Prefer Leistungszeitraum/document period labels and filename month patterns over first date token.</t>
+          <t>No parser fix required for sampled row.</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>65</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/04_Health_Insurance/02-2021 #9109.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/06_Bank_Payments/10. Nachweis von Lohnzahlungen - Bankkontoumsätze 2023.pdf</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>month; insurance_name; amount_due; amount_paid</t>
+          <t>month; insurance_name; amount_paid; unpaid_balance; due_date</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>{"month": "2021-02", "insurance_name": "AOK Plus", "amount_due": "1.02", "amount_paid": "25.01"}</t>
+          <t>{"month": "2023-01", "insurance_name": "AOK Plus", "amount_paid": "-67.93", "unpaid_balance": "1.05", "due_date": "29.03.2023"}</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -1867,7 +1867,7 @@
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>supported fields: month, insurance_name, amount_due, amount_paid; unsupported fields: none</t>
+          <t>supported fields: month, insurance_name, amount_paid, unpaid_balance, due_date; unsupported fields: none</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
@@ -1899,12 +1899,12 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>69</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/04_Health_Insurance/02-2023 #9109.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/06_Bank_Payments/Abstimmliste (DE - SEPA, Langform) (3) (1).pdf</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -1914,37 +1914,37 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>month; insurance_name; amount_due; amount_paid; unpaid_balance</t>
+          <t>month; insurance_name</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>{"month": "2023-03", "insurance_name": "AOK Plus", "amount_due": "-1316.88", "amount_paid": "28.02", "unpaid_balance": "1.23"}</t>
+          <t>{"month": "2025-01", "insurance_name": "AOK Plus"}</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>amount_due: not found</t>
+          <t>sampled values are supported by source text/path</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>CORRECT</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>supported fields: month, insurance_name, amount_paid, unpaid_balance; unsupported fields: amount_due</t>
+          <t>supported fields: month, insurance_name; unsupported fields: none</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>Extracted value was not directly found in the readable source text.</t>
+          <t/>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>Add field-specific validation patterns and source text snippets for this document type.</t>
+          <t>No parser fix required for sampled row.</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
@@ -1966,12 +1966,12 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>58</t>
+          <t>77</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/04_Health_Insurance/07-2022 #9109.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/06_Bank_Payments/SEPA-List health security.pdf</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -1981,12 +1981,12 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>month; insurance_name; amount_due; amount_paid; unpaid_balance</t>
+          <t>month; insurance_name</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>{"month": "2022-08", "insurance_name": "AOK Plus", "amount_due": "1.09", "amount_paid": "31.08", "unpaid_balance": "19.08"}</t>
+          <t>{"month": "2025-05", "insurance_name": "AOK Plus"}</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -2001,7 +2001,7 @@
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>supported fields: month, insurance_name, amount_due, amount_paid, unpaid_balance; unsupported fields: none</t>
+          <t>supported fields: month, insurance_name; unsupported fields: none</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
@@ -2033,12 +2033,12 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>63</t>
+          <t>78</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/04_Health_Insurance/12-2022 #9109.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/08_Operating_Costs/BWA 03-2025.pdf</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -2048,12 +2048,12 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>month; insurance_name; amount_due; amount_paid; unpaid_balance</t>
+          <t>month; insurance_name; amount_due</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>{"month": "2022-12", "insurance_name": "AOK Plus", "amount_due": "1.12", "amount_paid": "9.12", "unpaid_balance": "-23.43"}</t>
+          <t>{"month": "2025-03", "insurance_name": "TK", "amount_due": "801.50"}</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -2068,7 +2068,7 @@
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>supported fields: month, insurance_name, amount_due, amount_paid, unpaid_balance; unsupported fields: none</t>
+          <t>supported fields: month, insurance_name, amount_due; unsupported fields: none</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
@@ -2095,17 +2095,17 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Health Insurance</t>
+          <t>Tax</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>5</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/04_Health_Insurance/38389 - Vorgangsmappe Lohn - Contributions 28.05.2025.docx</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/02_Payroll/10001_03-2024_DivAuswertungen_DivMitarbeiter_8Z1.pdf</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -2115,12 +2115,12 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>month; insurance_name</t>
+          <t>tax_type; amount_due; amount_paid</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>{"month": "2025-05", "insurance_name": "AOK Plus"}</t>
+          <t>{"tax_type": "Lohnsteuer", "amount_due": "2413.55", "amount_paid": "0.00"}</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -2135,7 +2135,7 @@
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>supported fields: month, insurance_name; unsupported fields: none</t>
+          <t>supported fields: tax_type, amount_due, amount_paid; unsupported fields: none</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
@@ -2150,7 +2150,7 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>source read method: docx_xml</t>
+          <t>source read method: fitz</t>
         </is>
       </c>
     </row>
@@ -2162,17 +2162,17 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Health Insurance</t>
+          <t>Tax</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>68</t>
+          <t>7</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/04_Health_Insurance/Anforderung einer regelmäßigen Unbedenklichkeitsbescheinigung im Abonnement.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/02_Payroll/10001_04-2024_DivAuswertungen_DivMitarbeiter_BZ1.pdf</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -2182,12 +2182,12 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>insurance_name</t>
+          <t>tax_type; amount_due; amount_paid</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>{"insurance_name": "AOK"}</t>
+          <t>{"tax_type": "Lohnsteuer", "amount_due": "366.67", "amount_paid": "1548.00"}</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -2202,7 +2202,7 @@
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>supported fields: insurance_name; unsupported fields: none</t>
+          <t>supported fields: tax_type, amount_due, amount_paid; unsupported fields: none</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
@@ -2229,17 +2229,17 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Health Insurance</t>
+          <t>Tax</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>69</t>
+          <t>14</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/04_Health_Insurance/Antrag Freischaltung Mein AOK Arbeitgeberservice.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/02_Payroll/10001_09-2024_Brutto_NettoProbe_00051_QZ1.pdf</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -2249,12 +2249,12 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>month; insurance_name</t>
+          <t>tax_type</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>{"month": "2025-01", "insurance_name": "AOK Plus"}</t>
+          <t>{"tax_type": "Lohnsteuer"}</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -2269,7 +2269,7 @@
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>supported fields: month, insurance_name; unsupported fields: none</t>
+          <t>supported fields: tax_type; unsupported fields: none</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
@@ -2296,17 +2296,17 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Health Insurance</t>
+          <t>Tax</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>73</t>
+          <t>26</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/04_Health_Insurance/Contributions 13.03.2025.docx</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/03_Employee_Payslips/Entgeltbescheinigungen 01-2024.pdf</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -2316,12 +2316,12 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>month; insurance_name</t>
+          <t>month; creditor; tax_type; amount_due; amount_paid; due_date</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>{"month": "2025-03", "insurance_name": "AOK Plus"}</t>
+          <t>{"month": "2024-01", "creditor": "Finanzamt", "tax_type": "Lohnsteuer", "amount_due": "249.68", "amount_paid": "5889.13", "due_date": "29.01.2024"}</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -2336,7 +2336,7 @@
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>supported fields: month, insurance_name; unsupported fields: none</t>
+          <t>supported fields: month, creditor, tax_type, amount_due, amount_paid, due_date; unsupported fields: none</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
@@ -2351,7 +2351,7 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>source read method: docx_xml</t>
+          <t>source read method: fitz</t>
         </is>
       </c>
     </row>
@@ -2363,17 +2363,17 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Health Insurance</t>
+          <t>Tax</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>76</t>
+          <t>32</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/04_Health_Insurance/Remaining health insurances for 09_2024 und 10_2024.eml</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/03_Employee_Payslips/Entgeltbescheinigungen 04-2024.pdf</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -2383,12 +2383,12 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>month; insurance_name; amount_due</t>
+          <t>month; creditor; tax_type; amount_due; amount_paid; due_date</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>{"month": "2024-09", "insurance_name": "AOK Plus", "amount_due": "88.53"}</t>
+          <t>{"month": "2024-04", "creditor": "Finanzamt", "tax_type": "Lohnsteuer", "amount_due": "344.00", "amount_paid": "5689.02", "due_date": "26.04.2024"}</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -2403,7 +2403,7 @@
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>supported fields: month, insurance_name, amount_due; unsupported fields: none</t>
+          <t>supported fields: month, creditor, tax_type, amount_due, amount_paid, due_date; unsupported fields: none</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
@@ -2418,7 +2418,7 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>source read method: eml</t>
+          <t>source read method: fitz</t>
         </is>
       </c>
     </row>
@@ -2430,17 +2430,17 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Health Insurance</t>
+          <t>Tax</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>99</t>
+          <t>35</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/06_Bank_Payments/Abstimmliste (DE - SEPA, Langform) (1)__copy4.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/03_Employee_Payslips/Entgeltbescheinigungen 05-2025.pdf</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -2450,37 +2450,37 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>month; insurance_name; amount_due; amount_paid</t>
+          <t>month; creditor; tax_type; amount_paid; due_date</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>{"month": "2024-08", "insurance_name": "Hauptzollamt linked Krankenkasse claim", "amount_due": "52656.37", "amount_paid": "13.09"}</t>
+          <t>{"month": "2025-05", "creditor": "Finanzamt", "tax_type": "Lohnsteuer", "amount_paid": "4634.82", "due_date": "27.05.2025"}</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>amount_due: not found</t>
+          <t>sampled values are supported by source text/path</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>CORRECT</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>supported fields: month, amount_paid; unsupported fields: insurance_name, amount_due</t>
+          <t>supported fields: month, creditor, tax_type, amount_paid, due_date; unsupported fields: none</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>Extracted value was not directly found in the readable source text.</t>
+          <t/>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>Add field-specific validation patterns and source text snippets for this document type.</t>
+          <t>No parser fix required for sampled row.</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
@@ -2497,17 +2497,17 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Health Insurance</t>
+          <t>Tax</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>102</t>
+          <t>37</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/06_Bank_Payments/Abstimmliste (DE - SEPA, Langform) (2)__copy2.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/03_Employee_Payslips/Entgeltbescheinigungen 06-2025.pdf</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -2517,37 +2517,37 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>month; insurance_name; amount_due; amount_paid</t>
+          <t>month; creditor; tax_type; amount_paid; due_date</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>{"month": "2024-11", "insurance_name": "Hauptzollamt linked Krankenkasse claim", "amount_due": "1222.78", "amount_paid": "10.12"}</t>
+          <t>{"month": "2022-01", "creditor": "Finanzamt", "tax_type": "Lohnsteuer", "amount_paid": "2474.01", "due_date": "26.06.2025"}</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>amount_due: not found</t>
+          <t>sampled values are supported by source text/path</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>CORRECT</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>supported fields: month, amount_paid; unsupported fields: insurance_name, amount_due</t>
+          <t>supported fields: month, creditor, tax_type, amount_paid, due_date; unsupported fields: none</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>Extracted value was not directly found in the readable source text.</t>
+          <t/>
         </is>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>Add field-specific validation patterns and source text snippets for this document type.</t>
+          <t>No parser fix required for sampled row.</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
@@ -2564,17 +2564,17 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Health Insurance</t>
+          <t>Tax</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>114</t>
+          <t>50</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/06_Bank_Payments/SEPA List health security-1.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/04_Health_Insurance/07-2022 #9109.pdf</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -2584,17 +2584,17 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>month; insurance_name; amount_due; amount_paid</t>
+          <t>month; creditor; tax_type; amount_paid; unpaid_balance</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>{"month": "2025-03", "insurance_name": "AOK Plus", "amount_due": "1094.96", "amount_paid": "10.03"}</t>
+          <t>{"month": "2022-07", "creditor": "Finanzamt", "tax_type": "other public liability", "amount_paid": "-300.00", "unpaid_balance": "19.08"}</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>amount_due: not found</t>
+          <t>sampled values are supported by source text/path</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -2604,7 +2604,7 @@
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>supported fields: month, insurance_name, amount_paid; unsupported fields: amount_due</t>
+          <t>supported fields: month, creditor, amount_paid, unpaid_balance; unsupported fields: tax_type</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
@@ -2631,17 +2631,17 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Health Insurance</t>
+          <t>Tax</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>127</t>
+          <t>52</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/09_Enrico_Forwarded/Martin Zahariev Transporte 2055 07.02.2025 Sendungsverluste.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/04_Health_Insurance/10-2022 #9109.pdf</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -2651,12 +2651,12 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>month; insurance_name; amount_due</t>
+          <t>month; creditor; tax_type; amount_paid; unpaid_balance</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>{"month": "2055-07", "insurance_name": "TK", "amount_due": "12.11"}</t>
+          <t>{"month": "2022-10", "creditor": "Finanzamt", "tax_type": "other public liability", "amount_paid": "-1200.00", "unpaid_balance": "30.09"}</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -2666,22 +2666,22 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>WRONG</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>supported fields: insurance_name, amount_due; unsupported fields: month</t>
+          <t>supported fields: month, creditor, amount_paid, unpaid_balance; unsupported fields: tax_type</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>Month parser selected a nearby date or unrelated filename token.</t>
+          <t>Extracted value was not directly found in the readable source text.</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>Prefer Leistungszeitraum/document period labels and filename month patterns over first date token.</t>
+          <t>Add field-specific validation patterns and source text snippets for this document type.</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
@@ -2698,17 +2698,17 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Health Insurance</t>
+          <t>Tax</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>128</t>
+          <t>58</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/09_Enrico_Forwarded/Rechnung 2014 vom 05.12.2024 Sendungsverlust Zahariev.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/04_Health_Insurance/Arbeitsbescheinigung Georgi Stefanov.pdf</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -2718,12 +2718,12 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>month; insurance_name; amount_due</t>
+          <t>month; tax_type</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>{"month": "2024-12", "insurance_name": "DAK", "amount_due": "7.09"}</t>
+          <t>{"month": "2024-07", "tax_type": "Lohnsteuer"}</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -2738,7 +2738,7 @@
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>supported fields: month, insurance_name, amount_due; unsupported fields: none</t>
+          <t>supported fields: month, tax_type; unsupported fields: none</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
@@ -2753,7 +2753,7 @@
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>source read method: fitz</t>
+          <t>source read method: recovered_text</t>
         </is>
       </c>
     </row>
@@ -2770,12 +2770,12 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>64</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/02_Payroll/10001_03-2024_DivAuswertungen_DivMitarbeiter_8Z1.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/05_Taxes/41467 - Accountings 02-2024.pdf</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -2785,37 +2785,37 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>month; tax_type; amount_due; amount_paid</t>
+          <t>month; creditor; tax_type; amount_paid; unpaid_balance</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>{"month": "2024-11", "tax_type": "Lohnsteuer", "amount_due": "2413.55", "amount_paid": "11.04"}</t>
+          <t>{"month": "2024-02", "creditor": "Finanzamt", "tax_type": "Umsatzsteuer", "amount_paid": "18516.48", "unpaid_balance": "0.00"}</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>amount_due: not found</t>
+          <t>sampled values are supported by source text/path</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>WRONG</t>
+          <t>CORRECT</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>supported fields: tax_type, amount_paid; unsupported fields: month, amount_due</t>
+          <t>supported fields: month, creditor, tax_type, amount_paid, unpaid_balance; unsupported fields: none</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>Month parser selected a nearby date or unrelated filename token.</t>
+          <t/>
         </is>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>Prefer Leistungszeitraum/document period labels and filename month patterns over first date token.</t>
+          <t>No parser fix required for sampled row.</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
@@ -2837,12 +2837,12 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>65</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/02_Payroll/10001_04-2024_DivAuswertungen_DivMitarbeiter_BZ1.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/05_Taxes/90f3df27-1ca1-4b3a-9f1b-e33ffd37f10a.pdf</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -2852,37 +2852,37 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>month; tax_type; amount_due; amount_paid</t>
+          <t>month; tax_type; amount_due; amount_paid; unpaid_balance</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>{"month": "2024-08", "tax_type": "Lohnsteuer", "amount_due": "366.67", "amount_paid": "1548.00"}</t>
+          <t>{"month": "2023-10", "tax_type": "Umsatzsteuer", "amount_due": "19.00", "amount_paid": "1.60", "unpaid_balance": "20.00"}</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>amount_paid: not found</t>
+          <t>sampled values are supported by source text/path</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>WRONG</t>
+          <t>CORRECT</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>supported fields: tax_type, amount_due; unsupported fields: month, amount_paid</t>
+          <t>supported fields: month, tax_type, amount_due, amount_paid, unpaid_balance; unsupported fields: none</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>Month parser selected a nearby date or unrelated filename token.</t>
+          <t/>
         </is>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>Prefer Leistungszeitraum/document period labels and filename month patterns over first date token.</t>
+          <t>No parser fix required for sampled row.</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
@@ -2904,12 +2904,12 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>75</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/02_Payroll/10001_09-2024_Brutto_NettoProbe_00051_QZ1.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/05_Taxes/Accountings 11-2024.pdf</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>month; tax_type</t>
+          <t>month; creditor; tax_type; amount_paid; unpaid_balance</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>{"month": "2024-01", "tax_type": "Lohnsteuer"}</t>
+          <t>{"month": "2024-11", "creditor": "Finanzamt", "tax_type": "Umsatzsteuer", "amount_paid": "27948.98", "unpaid_balance": "0.00"}</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -2934,22 +2934,22 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>WRONG</t>
+          <t>CORRECT</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>supported fields: tax_type; unsupported fields: month</t>
+          <t>supported fields: month, creditor, tax_type, amount_paid, unpaid_balance; unsupported fields: none</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>Month parser selected a nearby date or unrelated filename token.</t>
+          <t/>
         </is>
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>Prefer Leistungszeitraum/document period labels and filename month patterns over first date token.</t>
+          <t>No parser fix required for sampled row.</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
@@ -2971,12 +2971,12 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>77</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/03_Employee_Payslips/Entgeltbescheinigungen 01-2024.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/05_Taxes/agb_doc.pdf</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -2986,37 +2986,37 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>month; creditor; tax_type; amount_due; amount_paid; due_date</t>
+          <t>tax_type</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>{"month": "2024-01", "creditor": "Finanzamt", "tax_type": "Lohnsteuer", "amount_due": "29.01", "amount_paid": "5889.13", "due_date": "29.01.2024"}</t>
+          <t>{"tax_type": "Umsatzsteuer"}</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>amount_paid: not found</t>
+          <t>sampled values are supported by source text/path</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>CORRECT</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>supported fields: month, creditor, tax_type, amount_due, due_date; unsupported fields: amount_paid</t>
+          <t>supported fields: tax_type; unsupported fields: none</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>Extracted value was not directly found in the readable source text.</t>
+          <t/>
         </is>
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>Add field-specific validation patterns and source text snippets for this document type.</t>
+          <t>No parser fix required for sampled row.</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
@@ -3038,12 +3038,12 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>90</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/03_Employee_Payslips/Entgeltbescheinigungen 04-2024.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/06_Bank_Payments/Abstimmliste (DE - SEPA, Langform) (3).pdf</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -3053,17 +3053,17 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>month; creditor; tax_type; amount_due; amount_paid; due_date</t>
+          <t>month; creditor; tax_type; amount_paid</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>{"month": "2024-04", "creditor": "Finanzamt", "tax_type": "Lohnsteuer", "amount_due": "26.04", "amount_paid": "5689.02", "due_date": "26.04.2024"}</t>
+          <t>{"month": "2024-02", "creditor": "Hauptzollamt", "tax_type": "other public liability", "amount_paid": "57567.96"}</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>amount_paid: not found</t>
+          <t>sampled values are supported by source text/path</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -3073,7 +3073,7 @@
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>supported fields: month, creditor, tax_type, amount_due, due_date; unsupported fields: amount_paid</t>
+          <t>supported fields: month, creditor, amount_paid; unsupported fields: tax_type</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
@@ -3105,12 +3105,12 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>92</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/03_Employee_Payslips/Entgeltbescheinigungen 06-2025.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/06_Bank_Payments/Abstimmliste (DE - SEPA, Langform).pdf</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -3120,37 +3120,37 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>month; creditor; tax_type; amount_due; amount_paid; due_date</t>
+          <t>month; creditor; tax_type; amount_paid</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>{"month": "2000-01", "creditor": "Finanzamt", "tax_type": "Lohnsteuer", "amount_due": "26.06", "amount_paid": "2474.01", "due_date": "26.06.2025"}</t>
+          <t>{"month": "2024-06", "creditor": "Hauptzollamt", "tax_type": "other public liability", "amount_paid": "54751.98"}</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>source filename month hint: 06-2025; amount_paid: not found</t>
+          <t>sampled values are supported by source text/path</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>WRONG</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>supported fields: creditor, tax_type, amount_due, due_date; unsupported fields: month, amount_paid</t>
+          <t>supported fields: month, creditor, amount_paid; unsupported fields: tax_type</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>Month parser selected a nearby date or unrelated filename token.</t>
+          <t>Extracted value was not directly found in the readable source text.</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>Prefer Leistungszeitraum/document period labels and filename month patterns over first date token.</t>
+          <t>Add field-specific validation patterns and source text snippets for this document type.</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
@@ -3172,12 +3172,12 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>95</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/04_Health_Insurance/06-2022 #9109.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/06_Bank_Payments/SEPA - Pfändungen.pdf</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -3187,17 +3187,17 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>month; creditor; tax_type; amount_due; amount_paid; unpaid_balance</t>
+          <t>month; creditor; tax_type; amount_paid</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>{"month": "2022-07", "creditor": "Finanzamt", "tax_type": "other public liability", "amount_due": "13665.11", "amount_paid": "4.07", "unpaid_balance": "-30.30"}</t>
+          <t>{"month": "2024-10", "creditor": "Hauptzollamt", "tax_type": "other public liability", "amount_paid": "1568.99"}</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>amount_due: not found</t>
+          <t>sampled values are supported by source text/path</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
@@ -3207,7 +3207,7 @@
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>supported fields: month, creditor, amount_paid, unpaid_balance; unsupported fields: tax_type, amount_due</t>
+          <t>supported fields: month, creditor, amount_paid; unsupported fields: tax_type</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
@@ -3239,12 +3239,12 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>96</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/04_Health_Insurance/07-2022 #9109.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/06_Bank_Payments/SEPA List seizures.pdf</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -3254,17 +3254,17 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>month; creditor; tax_type; amount_due; amount_paid; unpaid_balance</t>
+          <t>month; creditor; tax_type; amount_paid</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>{"month": "2022-08", "creditor": "Finanzamt", "tax_type": "other public liability", "amount_due": "9.09", "amount_paid": "31.08", "unpaid_balance": "19.08"}</t>
+          <t>{"month": "2025-02", "creditor": "Finanzamt", "tax_type": "other public liability", "amount_paid": "4654.34"}</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>sampled values are supported by source text/path</t>
+          <t>amount_paid: not found</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
@@ -3274,7 +3274,7 @@
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>supported fields: month, creditor, amount_due, amount_paid, unpaid_balance; unsupported fields: tax_type</t>
+          <t>supported fields: month, creditor; unsupported fields: tax_type, amount_paid</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
@@ -3306,12 +3306,12 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>58</t>
+          <t>99</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/04_Health_Insurance/12-2024_Brutto_Netto_00090_X0B.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/06_Bank_Payments/SEPA-List Seizures.pdf</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -3321,37 +3321,37 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>month; tax_type</t>
+          <t>month; creditor; tax_type; amount_paid</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>{"month": "2025-01", "tax_type": "Lohnsteuer"}</t>
+          <t>{"month": "2025-04", "creditor": "Finanzamt", "tax_type": "other public liability", "amount_paid": "3752.34"}</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>sampled values are supported by source text/path</t>
+          <t>amount_paid: not found</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>CORRECT</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>supported fields: month, tax_type; unsupported fields: none</t>
+          <t>supported fields: month, creditor; unsupported fields: tax_type, amount_paid</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t/>
+          <t>Extracted value was not directly found in the readable source text.</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>No parser fix required for sampled row.</t>
+          <t>Add field-specific validation patterns and source text snippets for this document type.</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
@@ -3373,12 +3373,12 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>64</t>
+          <t>114</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/04_Health_Insurance/Contributions 13.03.2025.docx</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/08_Operating_Costs/46851 - Rechnung 250303_2025 vom 31.03.2025, Aufträge 31_25, 33_25, 34_25, Mandant 42303.pdf</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -3388,12 +3388,12 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>month; creditor; tax_type</t>
+          <t>month; tax_type; amount_due; amount_paid; unpaid_balance</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>{"month": "2025-03", "creditor": "Hauptzollamt", "tax_type": "other public liability"}</t>
+          <t>{"month": "2025-03", "tax_type": "Umsatzsteuer", "amount_due": "19.00", "amount_paid": "1.88", "unpaid_balance": "20.00"}</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -3403,27 +3403,27 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>CORRECT</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>supported fields: month, creditor; unsupported fields: tax_type</t>
+          <t>supported fields: month, tax_type, amount_due, amount_paid, unpaid_balance; unsupported fields: none</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>Extracted value was not directly found in the readable source text.</t>
+          <t/>
         </is>
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>Add field-specific validation patterns and source text snippets for this document type.</t>
+          <t>No parser fix required for sampled row.</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>source read method: docx_xml</t>
+          <t>source read method: fitz</t>
         </is>
       </c>
     </row>
@@ -3435,17 +3435,17 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Tax</t>
+          <t>Operating Cost</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/04_Health_Insurance/Contributions 19.02.2025.docx</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/08_Operating_Costs/39739 - Rechnung 231128_2023 vom 28.12.2023, Aufträge 31_23, 32_23, 33_23, 34_23, 50_23, 98_23, Mandant 42303.pdf</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -3455,42 +3455,42 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>month; creditor; tax_type; amount_paid</t>
+          <t>month; category; amount_due; unpaid_balance</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>{"month": "2025-02", "creditor": "Hauptzollamt", "tax_type": "other public liability", "amount_paid": "13649.05"}</t>
+          <t>{"month": "2023-12", "category": "accounting fees", "amount_due": "20.00", "unpaid_balance": "20.00"}</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>amount_paid: not found</t>
+          <t>sampled values are supported by source text/path</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>CORRECT</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>supported fields: month, creditor; unsupported fields: tax_type, amount_paid</t>
+          <t>supported fields: month, category, amount_due, unpaid_balance; unsupported fields: none</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>Extracted value was not directly found in the readable source text.</t>
+          <t/>
         </is>
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>Add field-specific validation patterns and source text snippets for this document type.</t>
+          <t>No parser fix required for sampled row.</t>
         </is>
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>source read method: docx_xml</t>
+          <t>source read method: fitz</t>
         </is>
       </c>
     </row>
@@ -3502,17 +3502,17 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Tax</t>
+          <t>Operating Cost</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>4</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/05_Taxes/Accountings 02-2025.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/08_Operating_Costs/40579 - Rechnung 240155_2024 vom 17.02.2024, Aufträge 31_23, 33_23, 34_23, Mandant 42303.pdf</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -3522,37 +3522,37 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>month; creditor; tax_type; amount_due; amount_paid; unpaid_balance</t>
+          <t>month; category; amount_due; unpaid_balance</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>{"month": "2025-10", "creditor": "Finanzamt", "tax_type": "Umsatzsteuer", "amount_due": "13.36", "amount_paid": "0.00", "unpaid_balance": "10.04"}</t>
+          <t>{"month": "2024-02", "category": "accounting fees", "amount_due": "20.00", "unpaid_balance": "20.00"}</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>source filename month hint: 02-2025</t>
+          <t>sampled values are supported by source text/path</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>WRONG</t>
+          <t>CORRECT</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>supported fields: creditor, tax_type, amount_due, amount_paid, unpaid_balance; unsupported fields: month</t>
+          <t>supported fields: month, category, amount_due, unpaid_balance; unsupported fields: none</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>Month parser selected a nearby date or unrelated filename token.</t>
+          <t/>
         </is>
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>Prefer Leistungszeitraum/document period labels and filename month patterns over first date token.</t>
+          <t>No parser fix required for sampled row.</t>
         </is>
       </c>
       <c r="M53" t="inlineStr">
@@ -3569,17 +3569,17 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Tax</t>
+          <t>Operating Cost</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>5</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/05_Taxes/Accountings 05-2024.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/08_Operating_Costs/40850 - Rechnung 240213_2024 vom 29.01.2024, Aufträge 31_24, 32_23, 33_23, 33_24, 34_24, 98_24, Mandant 42303.pdf</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -3589,37 +3589,37 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>month; creditor; tax_type; amount_due; amount_paid; unpaid_balance</t>
+          <t>month; category; amount_due; unpaid_balance</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>{"month": "2024-11", "creditor": "Finanzamt", "tax_type": "Umsatzsteuer", "amount_due": "12.52", "amount_paid": "0.00", "unpaid_balance": "11.07"}</t>
+          <t>{"month": "2024-01", "category": "rent", "amount_due": "20.00", "unpaid_balance": "20.00"}</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>source filename month hint: 05-2024</t>
+          <t>sampled values are supported by source text/path</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>WRONG</t>
+          <t>CORRECT</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>supported fields: creditor, tax_type, amount_due, amount_paid, unpaid_balance; unsupported fields: month</t>
+          <t>supported fields: month, category, amount_due, unpaid_balance; unsupported fields: none</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>Month parser selected a nearby date or unrelated filename token.</t>
+          <t/>
         </is>
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>Prefer Leistungszeitraum/document period labels and filename month patterns over first date token.</t>
+          <t>No parser fix required for sampled row.</t>
         </is>
       </c>
       <c r="M54" t="inlineStr">
@@ -3636,17 +3636,17 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Tax</t>
+          <t>Operating Cost</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>8</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/06_Bank_Payments/10. Nachweis von Lohnzahlungen - Bankkontoumsätze 2024.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/08_Operating_Costs/42108 - Rechnung 240498_2024 vom 30.05.2024, Aufträge 21_24, 31_24, 32_24, 33_24, 34_24, Mandant 42303.pdf</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -3656,37 +3656,37 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>month; creditor; tax_type; amount_due; amount_paid; unpaid_balance</t>
+          <t>month; category; amount_due; unpaid_balance</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>{"month": "2002-01", "creditor": "Finanzamt", "tax_type": "other public liability", "amount_due": "4.01", "amount_paid": "3.01", "unpaid_balance": "68848.69"}</t>
+          <t>{"month": "2024-05", "category": "accounting fees", "amount_due": "20.00", "unpaid_balance": "20.00"}</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>unpaid_balance: not found</t>
+          <t>sampled values are supported by source text/path</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>WRONG</t>
+          <t>CORRECT</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>supported fields: creditor, amount_due, amount_paid; unsupported fields: month, tax_type, unpaid_balance</t>
+          <t>supported fields: month, category, amount_due, unpaid_balance; unsupported fields: none</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>Month parser selected a nearby date or unrelated filename token.</t>
+          <t/>
         </is>
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>Prefer Leistungszeitraum/document period labels and filename month patterns over first date token.</t>
+          <t>No parser fix required for sampled row.</t>
         </is>
       </c>
       <c r="M55" t="inlineStr">
@@ -3703,17 +3703,17 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Tax</t>
+          <t>Operating Cost</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>92</t>
+          <t>9</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/06_Bank_Payments/Abstimmliste (DE - SEPA, Langform) (1)__copy2.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/08_Operating_Costs/42585 - Rechnung 240587_2024 vom 29.06.2024, Aufträge 31_24, 33_23, 33_24, 34_24, Mandant 42303-1.pdf</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -3723,37 +3723,37 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>month; creditor; tax_type; amount_due; amount_paid</t>
+          <t>month; category; amount_due; unpaid_balance</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>{"month": "2024-05", "creditor": "Hauptzollamt", "tax_type": "other public liability", "amount_due": "54426.97", "amount_paid": "12.06"}</t>
+          <t>{"month": "2024-06", "category": "accounting fees", "amount_due": "20.00", "unpaid_balance": "20.00"}</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>amount_due: not found</t>
+          <t>sampled values are supported by source text/path</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>CORRECT</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>supported fields: month, creditor, amount_paid; unsupported fields: tax_type, amount_due</t>
+          <t>supported fields: month, category, amount_due, unpaid_balance; unsupported fields: none</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>Extracted value was not directly found in the readable source text.</t>
+          <t/>
         </is>
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>Add field-specific validation patterns and source text snippets for this document type.</t>
+          <t>No parser fix required for sampled row.</t>
         </is>
       </c>
       <c r="M56" t="inlineStr">
@@ -3770,17 +3770,17 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Tax</t>
+          <t>Operating Cost</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>95</t>
+          <t>14</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/06_Bank_Payments/Abstimmliste (DE - SEPA, Langform) (2)__copy2.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/08_Operating_Costs/45474 - Rechnung 241289_2024 vom 27.12.2024, Aufträge 21_24, 31_24, 32_24, 33_24, 34_24, 35_21, 35_24, 50_24, 98_24, Mandant 42303.pdf</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -3790,37 +3790,37 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>month; creditor; tax_type; amount_due; amount_paid</t>
+          <t>month; category; amount_due; unpaid_balance</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>{"month": "2024-11", "creditor": "Hauptzollamt", "tax_type": "other public liability", "amount_due": "1222.78", "amount_paid": "10.12"}</t>
+          <t>{"month": "2024-12", "category": "accounting fees", "amount_due": "20.00", "unpaid_balance": "20.00"}</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>amount_due: not found</t>
+          <t>sampled values are supported by source text/path</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>CORRECT</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>supported fields: month, creditor, amount_paid; unsupported fields: tax_type, amount_due</t>
+          <t>supported fields: month, category, amount_due, unpaid_balance; unsupported fields: none</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>Extracted value was not directly found in the readable source text.</t>
+          <t/>
         </is>
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>Add field-specific validation patterns and source text snippets for this document type.</t>
+          <t>No parser fix required for sampled row.</t>
         </is>
       </c>
       <c r="M57" t="inlineStr">
@@ -3837,17 +3837,17 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Tax</t>
+          <t>Operating Cost</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>96</t>
+          <t>16</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/06_Bank_Payments/Abstimmliste (DE - SEPA, Langform) (2)__copy3.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/08_Operating_Costs/46851 - Rechnung 250303_2025 vom 31.03.2025, Aufträge 31_25, 33_25, 34_25, Mandant 42303.pdf</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -3857,37 +3857,37 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>month; creditor; tax_type; amount_due; amount_paid</t>
+          <t>month; category; amount_due; unpaid_balance</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>{"month": "2024-01", "creditor": "Stadt Chemnitz", "tax_type": "other public liability", "amount_due": "56666.80", "amount_paid": "15.02"}</t>
+          <t>{"month": "2025-03", "category": "accounting fees", "amount_due": "20.00", "unpaid_balance": "20.00"}</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>amount_due: not found</t>
+          <t>sampled values are supported by source text/path</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>CORRECT</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>supported fields: month, creditor, amount_paid; unsupported fields: tax_type, amount_due</t>
+          <t>supported fields: month, category, amount_due, unpaid_balance; unsupported fields: none</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>Extracted value was not directly found in the readable source text.</t>
+          <t/>
         </is>
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>Add field-specific validation patterns and source text snippets for this document type.</t>
+          <t>No parser fix required for sampled row.</t>
         </is>
       </c>
       <c r="M58" t="inlineStr">
@@ -3904,17 +3904,17 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Tax</t>
+          <t>Operating Cost</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>99</t>
+          <t>17</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/06_Bank_Payments/Abstimmliste (DE - SEPA, Langform).pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/08_Operating_Costs/6106074_020725.pdf</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -3924,37 +3924,37 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>month; creditor; tax_type; amount_due; amount_paid</t>
+          <t>month; category; amount_due</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>{"month": "2024-06", "creditor": "Hauptzollamt", "tax_type": "other public liability", "amount_due": "54751.98", "amount_paid": "12.07"}</t>
+          <t>{"month": "2025-06", "category": "fuel", "amount_due": "5270.35"}</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>amount_due: not found</t>
+          <t>sampled values are supported by source text/path</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>CORRECT</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>supported fields: month, creditor, amount_paid; unsupported fields: tax_type, amount_due</t>
+          <t>supported fields: month, category, amount_due; unsupported fields: none</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>Extracted value was not directly found in the readable source text.</t>
+          <t/>
         </is>
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>Add field-specific validation patterns and source text snippets for this document type.</t>
+          <t>No parser fix required for sampled row.</t>
         </is>
       </c>
       <c r="M59" t="inlineStr">
@@ -3971,17 +3971,17 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Tax</t>
+          <t>Operating Cost</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>114</t>
+          <t>18</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/08_Operating_Costs/42585 - Rechnung 240587_2024 vom 29.06.2024, Aufträge 31_24, 33_23, 33_24, 34_24, Mandant 42303-1.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/08_Operating_Costs/6106074_040625.pdf</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -3991,12 +3991,12 @@
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>month; tax_type; amount_due; amount_paid; unpaid_balance</t>
+          <t>month; category; amount_due</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>{"month": "2024-06", "tax_type": "Umsatzsteuer", "amount_due": "19.00", "amount_paid": "1.77", "unpaid_balance": "20.00"}</t>
+          <t>{"month": "2025-05", "category": "fuel", "amount_due": "9949.77"}</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -4011,7 +4011,7 @@
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>supported fields: month, tax_type, amount_due, amount_paid, unpaid_balance; unsupported fields: none</t>
+          <t>supported fields: month, category, amount_due; unsupported fields: none</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
@@ -4038,17 +4038,17 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Tax</t>
+          <t>Operating Cost</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>115</t>
+          <t>19</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/08_Operating_Costs/43029 - Rechnung 240697_2024 vom 31.07.2024, Aufträge 21_23, 21_24, 31_22, 31_23, 31_24, 33_24, 34_24, Mandant 42303.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/08_Operating_Costs/6106074_050825.pdf</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -4058,12 +4058,12 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>month; tax_type; amount_due; amount_paid; unpaid_balance</t>
+          <t>month; category; amount_due</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>{"month": "2024-07", "tax_type": "Umsatzsteuer", "amount_due": "19.00", "amount_paid": "1.77", "unpaid_balance": "20.00"}</t>
+          <t>{"month": "2025-07", "category": "fuel", "amount_due": "1599.35"}</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -4078,7 +4078,7 @@
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>supported fields: month, tax_type, amount_due, amount_paid, unpaid_balance; unsupported fields: none</t>
+          <t>supported fields: month, category, amount_due; unsupported fields: none</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
@@ -4110,12 +4110,12 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>20</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/02_Payroll/10001_09-2024_DivAuswertungen_DivMitarbeiter_QZ1.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/08_Operating_Costs/6106074_061224.pdf</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -4125,37 +4125,37 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>month; category; amount_due; amount_paid</t>
+          <t>month; category; amount_due</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>{"month": "2024-09", "category": "insurance", "amount_due": "9.10", "amount_paid": "2236.00"}</t>
+          <t>{"month": "2024-11", "category": "fuel", "amount_due": "18535.34"}</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>amount_paid: not found</t>
+          <t>sampled values are supported by source text/path</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>CORRECT</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>supported fields: month, amount_due; unsupported fields: category, amount_paid</t>
+          <t>supported fields: month, category, amount_due; unsupported fields: none</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>Extracted value was not directly found in the readable source text.</t>
+          <t/>
         </is>
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>Add field-specific validation patterns and source text snippets for this document type.</t>
+          <t>No parser fix required for sampled row.</t>
         </is>
       </c>
       <c r="M62" t="inlineStr">
@@ -4177,12 +4177,12 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>26</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/02_Payroll/Lohnauswertungen_April_2025.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/08_Operating_Costs/Ihre Lohnauswertungen.eml</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -4192,42 +4192,42 @@
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>month; category; amount_due; amount_paid</t>
+          <t>month; category</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>{"month": "2025-05", "category": "insurance", "amount_due": "2196.75", "amount_paid": "2494.00"}</t>
+          <t>{"month": "2024-09", "category": "accounting fees"}</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>amount_due: not found; amount_paid: not found</t>
+          <t>sampled values are supported by source text/path</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>WRONG</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>supported fields: month; unsupported fields: category, amount_due, amount_paid</t>
+          <t>supported fields: category; unsupported fields: month</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>Extracted value was not directly found in the readable source text.</t>
+          <t>Month parser selected a nearby date or unrelated filename token.</t>
         </is>
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>Add field-specific validation patterns and source text snippets for this document type.</t>
+          <t>Prefer Leistungszeitraum/document period labels and filename month patterns over first date token.</t>
         </is>
       </c>
       <c r="M63" t="inlineStr">
         <is>
-          <t>source read method: fitz</t>
+          <t>source read method: eml</t>
         </is>
       </c>
     </row>
@@ -4244,12 +4244,12 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>27</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/02_Payroll/Lohnauswertungen_November_2024.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/08_Operating_Costs/Martin Zahariev Transporte 2036 08.01.2025 Scannermiete.pdf</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -4264,32 +4264,32 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>{"month": "2024-12", "category": "accounting fees", "amount_due": "1830.10"}</t>
+          <t>{"month": "2025-01", "category": "rent", "amount_due": "675.92"}</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>amount_due: not found</t>
+          <t>sampled values are supported by source text/path</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>CORRECT</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>supported fields: month; unsupported fields: category, amount_due</t>
+          <t>supported fields: month, category, amount_due; unsupported fields: none</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>Extracted value was not directly found in the readable source text.</t>
+          <t/>
         </is>
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>Add field-specific validation patterns and source text snippets for this document type.</t>
+          <t>No parser fix required for sampled row.</t>
         </is>
       </c>
       <c r="M64" t="inlineStr">
@@ -4311,12 +4311,12 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>28</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/03_Employee_Payslips/Entgeltbescheinigungen 06-2025.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/08_Operating_Costs/Martin Zahariev Transporte 2054 07.02.2025 Scannermiete.pdf</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
@@ -4326,37 +4326,37 @@
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>month; category; amount_due; amount_paid</t>
+          <t>month; category; amount_due</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>{"month": "2000-01", "category": "insurance", "amount_due": "4799.13", "amount_paid": "2474.01"}</t>
+          <t>{"month": "2025-02", "category": "rent", "amount_due": "637.84"}</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>source filename month hint: 06-2025; amount_due: not found; amount_paid: not found</t>
+          <t>sampled values are supported by source text/path</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>WRONG</t>
+          <t>CORRECT</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>supported fields: none; unsupported fields: month, category, amount_due, amount_paid</t>
+          <t>supported fields: month, category, amount_due; unsupported fields: none</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>Month parser selected a nearby date or unrelated filename token.</t>
+          <t/>
         </is>
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>Prefer Leistungszeitraum/document period labels and filename month patterns over first date token.</t>
+          <t>No parser fix required for sampled row.</t>
         </is>
       </c>
       <c r="M65" t="inlineStr">
@@ -4378,12 +4378,12 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>98</t>
+          <t>30</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/05_Taxes/38389 - Vorgangsmappe Lohn - 38389 - Aktualisiert- Auszahlungen Inflationsprämie.xlsx</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/08_Operating_Costs/Rechnung 2765 Zahariev Hermes Scannermiete.pdf</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
@@ -4393,12 +4393,12 @@
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>category</t>
+          <t>category; amount_due</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>{"category": "accounting fees"}</t>
+          <t>{"category": "rent", "amount_due": "637.84"}</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
@@ -4408,27 +4408,27 @@
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>CORRECT</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>supported fields: none; unsupported fields: category</t>
+          <t>supported fields: category, amount_due; unsupported fields: none</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>Extracted value was not directly found in the readable source text.</t>
+          <t/>
         </is>
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>Add field-specific validation patterns and source text snippets for this document type.</t>
+          <t>No parser fix required for sampled row.</t>
         </is>
       </c>
       <c r="M66" t="inlineStr">
         <is>
-          <t>source read method: xlsx_xml</t>
+          <t>source read method: fitz</t>
         </is>
       </c>
     </row>
@@ -4445,12 +4445,12 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>102</t>
+          <t>33</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/05_Taxes/90f3df27-1ca1-4b3a-9f1b-e33ffd37f10a.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/08_Operating_Costs/Rechnung 2782 Zahariev Hermes Bearbeitungsgebühr.pdf</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -4460,12 +4460,12 @@
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>month; category; amount_due; unpaid_balance</t>
+          <t>month; category; amount_due</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>{"month": "2023-10", "category": "insurance", "amount_due": "30.10", "unpaid_balance": "20.00"}</t>
+          <t>{"month": "2025-05", "category": "accounting fees", "amount_due": "35.70"}</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
@@ -4480,7 +4480,7 @@
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>supported fields: month, category, amount_due, unpaid_balance; unsupported fields: none</t>
+          <t>supported fields: month, category, amount_due; unsupported fields: none</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
@@ -4512,12 +4512,12 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>115</t>
+          <t>37</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/05_Taxes/Lohnauswertungen_August_2024.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/08_Operating_Costs/Rechnung 2799 Bearbeitungsgebühr 10.06.2025 Zahariev.pdf</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
@@ -4527,12 +4527,12 @@
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>month; category</t>
+          <t>month; category; amount_due</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>{"month": "2024-09", "category": "accounting fees"}</t>
+          <t>{"month": "2025-06", "category": "accounting fees", "amount_due": "53.55"}</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -4542,22 +4542,22 @@
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>CORRECT</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>supported fields: month; unsupported fields: category</t>
+          <t>supported fields: month, category, amount_due; unsupported fields: none</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>Extracted value was not directly found in the readable source text.</t>
+          <t/>
         </is>
       </c>
       <c r="L68" t="inlineStr">
         <is>
-          <t>Add field-specific validation patterns and source text snippets for this document type.</t>
+          <t>No parser fix required for sampled row.</t>
         </is>
       </c>
       <c r="M68" t="inlineStr">
@@ -4579,12 +4579,12 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>124</t>
+          <t>38</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/06_Bank_Payments/04-2022 #9120.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/08_Operating_Costs/Rechnung 2810 Zahariev TF Touren.pdf</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
@@ -4594,12 +4594,12 @@
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>month; category; amount_due</t>
+          <t>category; amount_due</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>{"month": "2022-04", "category": "vehicle costs", "amount_due": "9.05"}</t>
+          <t>{"category": "accounting fees", "amount_due": "9496.20"}</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
@@ -4609,22 +4609,22 @@
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>CORRECT</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>supported fields: month, amount_due; unsupported fields: category</t>
+          <t>supported fields: category, amount_due; unsupported fields: none</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>Extracted value was not directly found in the readable source text.</t>
+          <t/>
         </is>
       </c>
       <c r="L69" t="inlineStr">
         <is>
-          <t>Add field-specific validation patterns and source text snippets for this document type.</t>
+          <t>No parser fix required for sampled row.</t>
         </is>
       </c>
       <c r="M69" t="inlineStr">
@@ -4646,12 +4646,12 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>128</t>
+          <t>39</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/06_Bank_Payments/10. Nachweis von Lohnzahlungen - Bankkontoumsätze 2023.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/08_Operating_Costs/Rechnung 2811 Zahariev scannermiete.pdf</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
@@ -4661,12 +4661,12 @@
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>month; category; amount_due; unpaid_balance</t>
+          <t>category; amount_due</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>{"month": "2002-01", "category": "fuel", "amount_due": "49.94", "unpaid_balance": "-213.26"}</t>
+          <t>{"category": "rent", "amount_due": "333.20"}</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
@@ -4676,22 +4676,22 @@
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>WRONG</t>
+          <t>CORRECT</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>supported fields: amount_due, unpaid_balance; unsupported fields: month, category</t>
+          <t>supported fields: category, amount_due; unsupported fields: none</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>Month parser selected a nearby date or unrelated filename token.</t>
+          <t/>
         </is>
       </c>
       <c r="L70" t="inlineStr">
         <is>
-          <t>Prefer Leistungszeitraum/document period labels and filename month patterns over first date token.</t>
+          <t>No parser fix required for sampled row.</t>
         </is>
       </c>
       <c r="M70" t="inlineStr">
@@ -4713,12 +4713,12 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>134</t>
+          <t>49</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/06_Bank_Payments/Abstimmliste (DE - SEPA, Langform) (1)__copy2.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/08_Operating_Costs/Unternehmerabrechnung - VP 120-2400035414.pdf</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
@@ -4728,17 +4728,17 @@
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>month; category; amount_due</t>
+          <t>month; category; creditor; amount_due</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>{"month": "2024-05", "category": "accounting fees", "amount_due": "2060.70"}</t>
+          <t>{"month": "2024-01", "category": "fuel", "creditor": "en-Nr: 2000016306", "amount_due": "2543.30"}</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>amount_due: not found</t>
+          <t>sampled values are supported by source text/path</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
@@ -4748,7 +4748,7 @@
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>supported fields: month; unsupported fields: category, amount_due</t>
+          <t>supported fields: month, category, amount_due; unsupported fields: creditor</t>
         </is>
       </c>
       <c r="K71" t="inlineStr">
@@ -4775,17 +4775,17 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Operating Cost</t>
+          <t>Enrico</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>135</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/06_Bank_Payments/Abstimmliste (DE - SEPA, Langform) (1)__copy3.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/09_Enrico_Forwarded/gutschrift 05.04. 2025 zahariev.pdf</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
@@ -4795,37 +4795,37 @@
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>month; category; amount_due</t>
+          <t>month; document_number; document_type; amount</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>{"month": "2024-12", "category": "accounting fees", "amount_due": "2066.70"}</t>
+          <t>{"month": "2025-02", "document_number": "60-2025", "document_type": "Gutschrift", "amount": "75.91"}</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>amount_due: not found</t>
+          <t>sampled values are supported by source text/path</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>CORRECT</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>supported fields: month; unsupported fields: category, amount_due</t>
+          <t>supported fields: month, document_number, document_type, amount; unsupported fields: none</t>
         </is>
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>Extracted value was not directly found in the readable source text.</t>
+          <t/>
         </is>
       </c>
       <c r="L72" t="inlineStr">
         <is>
-          <t>Add field-specific validation patterns and source text snippets for this document type.</t>
+          <t>No parser fix required for sampled row.</t>
         </is>
       </c>
       <c r="M72" t="inlineStr">
@@ -4842,17 +4842,17 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Operating Cost</t>
+          <t>Enrico</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>136</t>
+          <t>4</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/06_Bank_Payments/Abstimmliste (DE - SEPA, Langform) (1)__copy4.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/09_Enrico_Forwarded/Gutschrift 24-2024 Zahariev Martin 31.07.2024.pdf</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
@@ -4862,37 +4862,37 @@
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>month; category; amount_due</t>
+          <t>month; document_number; document_type; amount</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>{"month": "2024-08", "category": "accounting fees", "amount_due": "1990.70"}</t>
+          <t>{"month": "2024-07", "document_number": "24-2024", "document_type": "Gutschrift", "amount": "179841.96"}</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>amount_due: not found</t>
+          <t>sampled values are supported by source text/path</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>CORRECT</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>supported fields: month; unsupported fields: category, amount_due</t>
+          <t>supported fields: month, document_number, document_type, amount; unsupported fields: none</t>
         </is>
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>Extracted value was not directly found in the readable source text.</t>
+          <t/>
         </is>
       </c>
       <c r="L73" t="inlineStr">
         <is>
-          <t>Add field-specific validation patterns and source text snippets for this document type.</t>
+          <t>No parser fix required for sampled row.</t>
         </is>
       </c>
       <c r="M73" t="inlineStr">
@@ -4909,17 +4909,17 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Operating Cost</t>
+          <t>Enrico</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>145</t>
+          <t>8</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/06_Bank_Payments/Abstimmliste (DE - SEPA, Langform).pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/09_Enrico_Forwarded/Gutschrift 42-2024 Zahariev Martin 30.11.2024.pdf</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
@@ -4929,37 +4929,37 @@
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>month; category; amount_due</t>
+          <t>month; document_number; document_type; amount</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>{"month": "2024-06", "category": "accounting fees", "amount_due": "2060.70"}</t>
+          <t>{"month": "2024-11", "document_number": "42-2024", "document_type": "Gutschrift", "amount": "232318.76"}</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>amount_due: not found</t>
+          <t>sampled values are supported by source text/path</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>CORRECT</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>supported fields: month; unsupported fields: category, amount_due</t>
+          <t>supported fields: month, document_number, document_type, amount; unsupported fields: none</t>
         </is>
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>Extracted value was not directly found in the readable source text.</t>
+          <t/>
         </is>
       </c>
       <c r="L74" t="inlineStr">
         <is>
-          <t>Add field-specific validation patterns and source text snippets for this document type.</t>
+          <t>No parser fix required for sampled row.</t>
         </is>
       </c>
       <c r="M74" t="inlineStr">
@@ -4976,17 +4976,17 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Operating Cost</t>
+          <t>Enrico</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>150</t>
+          <t>9</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/06_Bank_Payments/Favorit MP Martin Zahariev _4025268_vom_01.09.2024.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/09_Enrico_Forwarded/Gutschrift 44-2024 Zahariev Martin 31.12.2024.pdf</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
@@ -4996,12 +4996,12 @@
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>month; category; creditor; amount_due</t>
+          <t>month; document_number; document_type; amount</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>{"month": "2024-09", "category": "phone", "creditor": "-Id", "amount_due": "10.99"}</t>
+          <t>{"month": "2024-12", "document_number": "44-2024", "document_type": "Gutschrift", "amount": "188941.38"}</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
@@ -5011,22 +5011,22 @@
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>CORRECT</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>supported fields: month, creditor, amount_due; unsupported fields: category</t>
+          <t>supported fields: month, document_number, document_type, amount; unsupported fields: none</t>
         </is>
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>Extracted value was not directly found in the readable source text.</t>
+          <t/>
         </is>
       </c>
       <c r="L75" t="inlineStr">
         <is>
-          <t>Add field-specific validation patterns and source text snippets for this document type.</t>
+          <t>No parser fix required for sampled row.</t>
         </is>
       </c>
       <c r="M75" t="inlineStr">
@@ -5043,17 +5043,17 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Operating Cost</t>
+          <t>Enrico</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>196</t>
+          <t>10</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/08_Operating_Costs/42108 - Rechnung 240498_2024 vom 30.05.2024, Aufträge 21_24, 31_24, 32_24, 33_24, 34_24, Mandant 42303.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/09_Enrico_Forwarded/gutschrift 66 Mai 2025 zahariev.pdf</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
@@ -5063,12 +5063,12 @@
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>month; category; amount_due; unpaid_balance</t>
+          <t>month; document_number; document_type; amount</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>{"month": "2024-05", "category": "insurance", "amount_due": "30.05", "unpaid_balance": "20.00"}</t>
+          <t>{"month": "2025-05", "document_number": "66-2025", "document_type": "Gutschrift", "amount": "120491.84"}</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
@@ -5083,7 +5083,7 @@
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>supported fields: month, category, amount_due, unpaid_balance; unsupported fields: none</t>
+          <t>supported fields: month, document_number, document_type, amount; unsupported fields: none</t>
         </is>
       </c>
       <c r="K76" t="inlineStr">
@@ -5110,17 +5110,17 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Operating Cost</t>
+          <t>Enrico</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>202</t>
+          <t>14</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/08_Operating_Costs/45474 - Rechnung 241289_2024 vom 27.12.2024, Aufträge 21_24, 31_24, 32_24, 33_24, 34_24, 35_21, 35_24, 50_24, 98_24, Mandant 42303.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/09_Enrico_Forwarded/Gutschrift Zahariev 74 30.06.2025.pdf</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
@@ -5130,12 +5130,12 @@
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>month; category; amount_due; unpaid_balance</t>
+          <t>month; document_number; document_type; amount</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>{"month": "2024-12", "category": "insurance", "amount_due": "27.12", "unpaid_balance": "20.00"}</t>
+          <t>{"month": "2025-06", "document_number": "74-2025", "document_type": "Gutschrift", "amount": "55392.95"}</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
@@ -5150,7 +5150,7 @@
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>supported fields: month, category, amount_due, unpaid_balance; unsupported fields: none</t>
+          <t>supported fields: month, document_number, document_type, amount; unsupported fields: none</t>
         </is>
       </c>
       <c r="K77" t="inlineStr">
@@ -5177,17 +5177,17 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Operating Cost</t>
+          <t>Enrico</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>227</t>
+          <t>17</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/08_Operating_Costs/Rechnung 2811 Zahariev scannermiete.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/09_Enrico_Forwarded/Leistungsnachweis Martin Zahariev Januar 2025.pdf</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
@@ -5197,12 +5197,12 @@
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>month; category; amount_due</t>
+          <t>month</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>{"month": "2025-07", "category": "rent", "amount_due": "333.20"}</t>
+          <t>{"month": "2025-01"}</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
@@ -5212,22 +5212,22 @@
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>CORRECT</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>supported fields: month, amount_due; unsupported fields: category</t>
+          <t>supported fields: month; unsupported fields: none</t>
         </is>
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>Extracted value was not directly found in the readable source text.</t>
+          <t/>
         </is>
       </c>
       <c r="L78" t="inlineStr">
         <is>
-          <t>Add field-specific validation patterns and source text snippets for this document type.</t>
+          <t>No parser fix required for sampled row.</t>
         </is>
       </c>
       <c r="M78" t="inlineStr">
@@ -5244,17 +5244,17 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Operating Cost</t>
+          <t>Enrico</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>253</t>
+          <t>18</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/09_Enrico_Forwarded/Leistungsnachweis Martin Zahariev Februar 2025.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/09_Enrico_Forwarded/Leistungsnachweis November 2024.pdf</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
@@ -5264,12 +5264,12 @@
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>month; category; amount_due</t>
+          <t>month</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>{"month": "2025-02", "category": "accounting fees", "amount_due": "1.02"}</t>
+          <t>{"month": "2024-11"}</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
@@ -5279,22 +5279,22 @@
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>CORRECT</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>supported fields: month, amount_due; unsupported fields: category</t>
+          <t>supported fields: month; unsupported fields: none</t>
         </is>
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>Extracted value was not directly found in the readable source text.</t>
+          <t/>
         </is>
       </c>
       <c r="L79" t="inlineStr">
         <is>
-          <t>Add field-specific validation patterns and source text snippets for this document type.</t>
+          <t>No parser fix required for sampled row.</t>
         </is>
       </c>
       <c r="M79" t="inlineStr">
@@ -5311,17 +5311,17 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Operating Cost</t>
+          <t>Enrico</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>255</t>
+          <t>19</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/09_Enrico_Forwarded/Leistungsnachweis November 2024.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/09_Enrico_Forwarded/Leistungsnachweis Oktober 2024.pdf</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
@@ -5331,12 +5331,12 @@
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>month; category; amount_due</t>
+          <t>month</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>{"month": "2024-11", "category": "accounting fees", "amount_due": "1.11"}</t>
+          <t>{"month": "2024-10"}</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
@@ -5346,22 +5346,22 @@
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>CORRECT</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>supported fields: month, amount_due; unsupported fields: category</t>
+          <t>supported fields: month; unsupported fields: none</t>
         </is>
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t>Extracted value was not directly found in the readable source text.</t>
+          <t/>
         </is>
       </c>
       <c r="L80" t="inlineStr">
         <is>
-          <t>Add field-specific validation patterns and source text snippets for this document type.</t>
+          <t>No parser fix required for sampled row.</t>
         </is>
       </c>
       <c r="M80" t="inlineStr">
@@ -5378,32 +5378,32 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Operating Cost</t>
+          <t>Enrico</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>296</t>
+          <t>20</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/03_Employee_Payslips/8. Lohnabrechnungen aller Mitarbeiter.zip</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/09_Enrico_Forwarded/Leistungsnachweis September 2024.pdf</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>month; category</t>
+          <t>month</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>{"month": "2023-10", "category": "accounting fees"}</t>
+          <t>{"month": "2024-09"}</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
@@ -5413,27 +5413,27 @@
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>WRONG</t>
+          <t>CORRECT</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>supported fields: none; unsupported fields: month, category</t>
+          <t>supported fields: month; unsupported fields: none</t>
         </is>
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t>Month parser selected a nearby date or unrelated filename token.</t>
+          <t/>
         </is>
       </c>
       <c r="L81" t="inlineStr">
         <is>
-          <t>Prefer Leistungszeitraum/document period labels and filename month patterns over first date token.</t>
+          <t>No parser fix required for sampled row.</t>
         </is>
       </c>
       <c r="M81" t="inlineStr">
         <is>
-          <t>source read method: unsupported source type: .zip</t>
+          <t>source read method: fitz</t>
         </is>
       </c>
     </row>
@@ -5450,12 +5450,12 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>24</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/04_Health_Insurance/04-2021 #9109.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/09_Enrico_Forwarded/Leistungsnachweis Zahariev Juni 25 Sachsenpower GmbH &amp; Co. KG.pdf</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
@@ -5465,37 +5465,37 @@
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>month; document_number; document_type; amount</t>
+          <t>month</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>{"month": "2021-04", "document_number": "1637805507", "document_type": "Gutschrift", "amount": "12.04"}</t>
+          <t>{"month": "2025-05"}</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>source is not in Enrico_Forwarded category</t>
+          <t>sampled values are supported by source text/path</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>WRONG</t>
+          <t>CORRECT</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>supported fields: month, document_number, document_type, amount; unsupported fields: none</t>
+          <t>supported fields: month; unsupported fields: none</t>
         </is>
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t>Enrico detector is too broad and accepts non-Enrico health-insurance/accounting documents.</t>
+          <t/>
         </is>
       </c>
       <c r="L82" t="inlineStr">
         <is>
-          <t>Restrict category detection to folder hints plus stronger Enrico/Sachsenpower terms.</t>
+          <t>No parser fix required for sampled row.</t>
         </is>
       </c>
       <c r="M82" t="inlineStr">
@@ -5517,12 +5517,12 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>26</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/04_Health_Insurance/06-2021 #9109.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/09_Enrico_Forwarded/Martin Zahariev Gutschrift 48 31.01.2025.pdf</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
@@ -5532,37 +5532,37 @@
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>month; document_type; amount</t>
+          <t>month; document_number; document_type; amount</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>{"month": "2021-06", "document_type": "Gutschrift", "amount": "11.06"}</t>
+          <t>{"month": "2025-01", "document_number": "48-2025", "document_type": "Gutschrift", "amount": "189578.90"}</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>source is not in Enrico_Forwarded category</t>
+          <t>sampled values are supported by source text/path</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>WRONG</t>
+          <t>CORRECT</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>supported fields: month, document_type, amount; unsupported fields: none</t>
+          <t>supported fields: month, document_number, document_type, amount; unsupported fields: none</t>
         </is>
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t>Enrico detector is too broad and accepts non-Enrico health-insurance/accounting documents.</t>
+          <t/>
         </is>
       </c>
       <c r="L83" t="inlineStr">
         <is>
-          <t>Restrict category detection to folder hints plus stronger Enrico/Sachsenpower terms.</t>
+          <t>No parser fix required for sampled row.</t>
         </is>
       </c>
       <c r="M83" t="inlineStr">
@@ -5584,12 +5584,12 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>27</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/04_Health_Insurance/07-2021 #9109.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/09_Enrico_Forwarded/Martin Zahariev Gutschrift 51 17.02.2025.pdf</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
@@ -5599,37 +5599,37 @@
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>month; document_type; amount</t>
+          <t>month; document_number; document_type; amount</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>{"month": "2021-07", "document_type": "Gutschrift", "amount": "14.07"}</t>
+          <t>{"month": "2024-11", "document_number": "51-2025", "document_type": "Gutschrift", "amount": "100.00"}</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>source is not in Enrico_Forwarded category</t>
+          <t>sampled values are supported by source text/path</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>WRONG</t>
+          <t>CORRECT</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>supported fields: month, document_type, amount; unsupported fields: none</t>
+          <t>supported fields: month, document_number, document_type, amount; unsupported fields: none</t>
         </is>
       </c>
       <c r="K84" t="inlineStr">
         <is>
-          <t>Enrico detector is too broad and accepts non-Enrico health-insurance/accounting documents.</t>
+          <t/>
         </is>
       </c>
       <c r="L84" t="inlineStr">
         <is>
-          <t>Restrict category detection to folder hints plus stronger Enrico/Sachsenpower terms.</t>
+          <t>No parser fix required for sampled row.</t>
         </is>
       </c>
       <c r="M84" t="inlineStr">
@@ -5651,12 +5651,12 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>30</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/04_Health_Insurance/12-2021 #9109.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/09_Enrico_Forwarded/Martin Zahariev Transporte 2035 08.01.2025 Hermes Bekleidung.pdf</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
@@ -5666,37 +5666,37 @@
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>month; document_type; amount</t>
+          <t>month; document_number; document_type; amount</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>{"month": "2021-12", "document_type": "Gutschrift", "amount": "27.12"}</t>
+          <t>{"month": "2025-01", "document_number": "02035", "document_type": "Rechnung", "amount": "38.00"}</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>source is not in Enrico_Forwarded category</t>
+          <t>sampled values are supported by source text/path</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>WRONG</t>
+          <t>CORRECT</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>supported fields: month, document_type, amount; unsupported fields: none</t>
+          <t>supported fields: month, document_number, document_type, amount; unsupported fields: none</t>
         </is>
       </c>
       <c r="K85" t="inlineStr">
         <is>
-          <t>Enrico detector is too broad and accepts non-Enrico health-insurance/accounting documents.</t>
+          <t/>
         </is>
       </c>
       <c r="L85" t="inlineStr">
         <is>
-          <t>Restrict category detection to folder hints plus stronger Enrico/Sachsenpower terms.</t>
+          <t>No parser fix required for sampled row.</t>
         </is>
       </c>
       <c r="M85" t="inlineStr">
@@ -5718,12 +5718,12 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>31</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/06_Bank_Payments/Zahlungsavis Zahariev Juni 2025.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/09_Enrico_Forwarded/Martin Zahariev Transporte 2037 08.01.2025 Sendungsverluste.pdf</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
@@ -5738,17 +5738,17 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>{"month": "2025-07", "document_number": "2810", "document_type": "Rechnung", "amount": "30.06"}</t>
+          <t>{"month": "2025-01", "document_number": "02037", "document_type": "Rechnung", "amount": "11648.45"}</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>source is not in Enrico_Forwarded category</t>
+          <t>sampled values are supported by source text/path</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>WRONG</t>
+          <t>CORRECT</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
@@ -5758,12 +5758,12 @@
       </c>
       <c r="K86" t="inlineStr">
         <is>
-          <t>Enrico detector is too broad and accepts non-Enrico health-insurance/accounting documents.</t>
+          <t/>
         </is>
       </c>
       <c r="L86" t="inlineStr">
         <is>
-          <t>Restrict category detection to folder hints plus stronger Enrico/Sachsenpower terms.</t>
+          <t>No parser fix required for sampled row.</t>
         </is>
       </c>
       <c r="M86" t="inlineStr">
@@ -5785,12 +5785,12 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>33</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/08_Operating_Costs/Rechnung 2765 Zahariev Hermes Scannermiete.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/09_Enrico_Forwarded/Martin Zahariev Transporte 2055 07.02.2025 Sendungsverluste.pdf</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
@@ -5805,17 +5805,17 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>{"month": "2025-04", "document_number": "02765", "document_type": "Rechnung", "amount": "637.84"}</t>
+          <t>{"month": "2025-02", "document_number": "02055", "document_type": "Rechnung", "amount": "7847.85"}</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>source is not in Enrico_Forwarded category</t>
+          <t>sampled values are supported by source text/path</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>WRONG</t>
+          <t>CORRECT</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
@@ -5825,12 +5825,12 @@
       </c>
       <c r="K87" t="inlineStr">
         <is>
-          <t>Enrico detector is too broad and accepts non-Enrico health-insurance/accounting documents.</t>
+          <t/>
         </is>
       </c>
       <c r="L87" t="inlineStr">
         <is>
-          <t>Restrict category detection to folder hints plus stronger Enrico/Sachsenpower terms.</t>
+          <t>No parser fix required for sampled row.</t>
         </is>
       </c>
       <c r="M87" t="inlineStr">
@@ -5852,12 +5852,12 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>35</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/08_Operating_Costs/Rechnung 2778 Zahariev Hermes Scannermiete.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/09_Enrico_Forwarded/Martin Zahariev Transporte 2057 07.02.2025 Hermes Bekleidung.pdf</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
@@ -5872,17 +5872,17 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>{"month": "2025-05", "document_number": "02778", "document_type": "Rechnung", "amount": "599.76"}</t>
+          <t>{"month": "2025-02", "document_number": "02057", "document_type": "Rechnung", "amount": "94.52"}</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>source is not in Enrico_Forwarded category</t>
+          <t>sampled values are supported by source text/path</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>WRONG</t>
+          <t>CORRECT</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
@@ -5892,12 +5892,12 @@
       </c>
       <c r="K88" t="inlineStr">
         <is>
-          <t>Enrico detector is too broad and accepts non-Enrico health-insurance/accounting documents.</t>
+          <t/>
         </is>
       </c>
       <c r="L88" t="inlineStr">
         <is>
-          <t>Restrict category detection to folder hints plus stronger Enrico/Sachsenpower terms.</t>
+          <t>No parser fix required for sampled row.</t>
         </is>
       </c>
       <c r="M88" t="inlineStr">
@@ -5919,12 +5919,12 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>39</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/08_Operating_Costs/Rechnung 2789 Zahariev TF Touren.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/09_Enrico_Forwarded/Rechnung 2015 07.12.2024 Martin Zahariev.pdf</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
@@ -5939,32 +5939,32 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>{"month": "2025-06", "document_number": "02789", "document_type": "Rechnung", "amount": "8282.40"}</t>
+          <t>{"month": "2024-12", "document_number": "02015", "document_type": "Rechnung", "amount": "196.35"}</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>amount: not found; source is not in Enrico_Forwarded category</t>
+          <t>sampled values are supported by source text/path</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>WRONG</t>
+          <t>CORRECT</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>supported fields: month, document_number, document_type; unsupported fields: amount</t>
+          <t>supported fields: month, document_number, document_type, amount; unsupported fields: none</t>
         </is>
       </c>
       <c r="K89" t="inlineStr">
         <is>
-          <t>Enrico detector is too broad and accepts non-Enrico health-insurance/accounting documents.</t>
+          <t/>
         </is>
       </c>
       <c r="L89" t="inlineStr">
         <is>
-          <t>Restrict category detection to folder hints plus stronger Enrico/Sachsenpower terms.</t>
+          <t>No parser fix required for sampled row.</t>
         </is>
       </c>
       <c r="M89" t="inlineStr">
@@ -5986,12 +5986,12 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>43</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/08_Operating_Costs/Rechnung 2799 Bearbeitungsgebühr 10.06.2025 Zahariev.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/09_Enrico_Forwarded/Rechnung 2767 Zahariev Hermes Bearbeitungsgebuhr.pdf</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
@@ -6006,17 +6006,17 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>{"month": "2025-06", "document_number": "02799", "document_type": "Rechnung", "amount": "53.55"}</t>
+          <t>{"month": "2025-04", "document_number": "02767", "document_type": "Rechnung", "amount": "50.58"}</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>source is not in Enrico_Forwarded category</t>
+          <t>sampled values are supported by source text/path</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>WRONG</t>
+          <t>CORRECT</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
@@ -6026,12 +6026,12 @@
       </c>
       <c r="K90" t="inlineStr">
         <is>
-          <t>Enrico detector is too broad and accepts non-Enrico health-insurance/accounting documents.</t>
+          <t/>
         </is>
       </c>
       <c r="L90" t="inlineStr">
         <is>
-          <t>Restrict category detection to folder hints plus stronger Enrico/Sachsenpower terms.</t>
+          <t>No parser fix required for sampled row.</t>
         </is>
       </c>
       <c r="M90" t="inlineStr">
@@ -6053,12 +6053,12 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>45</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/08_Operating_Costs/Rechnung 2811 Zahariev scannermiete.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/09_Enrico_Forwarded/Rechnung 2798 Zahariev Hermes Sendungsverlust.pdf</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
@@ -6068,710 +6068,40 @@
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>month; document_number; document_type; amount</t>
+          <t>document_number; document_type; amount</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>{"month": "2025-07", "document_number": "02811", "document_type": "Rechnung", "amount": "333.20"}</t>
+          <t>{"document_number": "02798", "document_type": "Rechnung", "amount": "3042.12"}</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>source is not in Enrico_Forwarded category</t>
+          <t>sampled values are supported by source text/path</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>WRONG</t>
+          <t>CORRECT</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>supported fields: month, document_number, document_type, amount; unsupported fields: none</t>
+          <t>supported fields: document_number, document_type, amount; unsupported fields: none</t>
         </is>
       </c>
       <c r="K91" t="inlineStr">
         <is>
-          <t>Enrico detector is too broad and accepts non-Enrico health-insurance/accounting documents.</t>
+          <t/>
         </is>
       </c>
       <c r="L91" t="inlineStr">
         <is>
-          <t>Restrict category detection to folder hints plus stronger Enrico/Sachsenpower terms.</t>
+          <t>No parser fix required for sampled row.</t>
         </is>
       </c>
       <c r="M91" t="inlineStr">
-        <is>
-          <t>source read method: fitz</t>
-        </is>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" t="inlineStr">
-        <is>
-          <t>VAL-0091</t>
-        </is>
-      </c>
-      <c r="B92" t="inlineStr">
-        <is>
-          <t>Enrico</t>
-        </is>
-      </c>
-      <c r="C92" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="D92" t="inlineStr">
-        <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/08_Operating_Costs/Unternehmerabrechnung - VP 120-2400035649.pdf</t>
-        </is>
-      </c>
-      <c r="E92" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="F92" t="inlineStr">
-        <is>
-          <t>month; document_number; document_type; document_date; amount</t>
-        </is>
-      </c>
-      <c r="G92" t="inlineStr">
-        <is>
-          <t>{"month": "2024-01", "document_number": "120-2400035649", "document_type": "GUTSCHRIFT", "document_date": "26.03.2024", "amount": "608.64"}</t>
-        </is>
-      </c>
-      <c r="H92" t="inlineStr">
-        <is>
-          <t>source is not in Enrico_Forwarded category</t>
-        </is>
-      </c>
-      <c r="I92" t="inlineStr">
-        <is>
-          <t>WRONG</t>
-        </is>
-      </c>
-      <c r="J92" t="inlineStr">
-        <is>
-          <t>supported fields: month, document_number, document_type, document_date, amount; unsupported fields: none</t>
-        </is>
-      </c>
-      <c r="K92" t="inlineStr">
-        <is>
-          <t>Enrico detector is too broad and accepts non-Enrico health-insurance/accounting documents.</t>
-        </is>
-      </c>
-      <c r="L92" t="inlineStr">
-        <is>
-          <t>Restrict category detection to folder hints plus stronger Enrico/Sachsenpower terms.</t>
-        </is>
-      </c>
-      <c r="M92" t="inlineStr">
-        <is>
-          <t>source read method: fitz</t>
-        </is>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" t="inlineStr">
-        <is>
-          <t>VAL-0092</t>
-        </is>
-      </c>
-      <c r="B93" t="inlineStr">
-        <is>
-          <t>Enrico</t>
-        </is>
-      </c>
-      <c r="C93" t="inlineStr">
-        <is>
-          <t>52</t>
-        </is>
-      </c>
-      <c r="D93" t="inlineStr">
-        <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/09_Enrico_Forwarded/gutschrift 05.04. 2025 zahariev.pdf</t>
-        </is>
-      </c>
-      <c r="E93" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="F93" t="inlineStr">
-        <is>
-          <t>month; document_number; document_type; amount</t>
-        </is>
-      </c>
-      <c r="G93" t="inlineStr">
-        <is>
-          <t>{"month": "2025-04", "document_number": "60-2025", "document_type": "Gutschrift", "amount": "75.91"}</t>
-        </is>
-      </c>
-      <c r="H93" t="inlineStr">
-        <is>
-          <t>sampled values are supported by source text/path</t>
-        </is>
-      </c>
-      <c r="I93" t="inlineStr">
-        <is>
-          <t>CORRECT</t>
-        </is>
-      </c>
-      <c r="J93" t="inlineStr">
-        <is>
-          <t>supported fields: month, document_number, document_type, amount; unsupported fields: none</t>
-        </is>
-      </c>
-      <c r="K93" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="L93" t="inlineStr">
-        <is>
-          <t>No parser fix required for sampled row.</t>
-        </is>
-      </c>
-      <c r="M93" t="inlineStr">
-        <is>
-          <t>source read method: fitz</t>
-        </is>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" t="inlineStr">
-        <is>
-          <t>VAL-0093</t>
-        </is>
-      </c>
-      <c r="B94" t="inlineStr">
-        <is>
-          <t>Enrico</t>
-        </is>
-      </c>
-      <c r="C94" t="inlineStr">
-        <is>
-          <t>58</t>
-        </is>
-      </c>
-      <c r="D94" t="inlineStr">
-        <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/09_Enrico_Forwarded/Gutschrift 44-2024 Zahariev Martin 31.12.2024.pdf</t>
-        </is>
-      </c>
-      <c r="E94" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="F94" t="inlineStr">
-        <is>
-          <t>month; document_number; document_type; amount</t>
-        </is>
-      </c>
-      <c r="G94" t="inlineStr">
-        <is>
-          <t>{"month": "2024-12", "document_number": "44-2024", "document_type": "Gutschrift", "amount": "188941.38"}</t>
-        </is>
-      </c>
-      <c r="H94" t="inlineStr">
-        <is>
-          <t>amount: not found</t>
-        </is>
-      </c>
-      <c r="I94" t="inlineStr">
-        <is>
-          <t>PARTIAL</t>
-        </is>
-      </c>
-      <c r="J94" t="inlineStr">
-        <is>
-          <t>supported fields: month, document_number, document_type; unsupported fields: amount</t>
-        </is>
-      </c>
-      <c r="K94" t="inlineStr">
-        <is>
-          <t>Extracted value was not directly found in the readable source text.</t>
-        </is>
-      </c>
-      <c r="L94" t="inlineStr">
-        <is>
-          <t>Add field-specific validation patterns and source text snippets for this document type.</t>
-        </is>
-      </c>
-      <c r="M94" t="inlineStr">
-        <is>
-          <t>source read method: fitz</t>
-        </is>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" t="inlineStr">
-        <is>
-          <t>VAL-0094</t>
-        </is>
-      </c>
-      <c r="B95" t="inlineStr">
-        <is>
-          <t>Enrico</t>
-        </is>
-      </c>
-      <c r="C95" t="inlineStr">
-        <is>
-          <t>64</t>
-        </is>
-      </c>
-      <c r="D95" t="inlineStr">
-        <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/09_Enrico_Forwarded/Leistungsnachweis Dezember Zahariev 2024.pdf</t>
-        </is>
-      </c>
-      <c r="E95" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="F95" t="inlineStr">
-        <is>
-          <t>month</t>
-        </is>
-      </c>
-      <c r="G95" t="inlineStr">
-        <is>
-          <t>{"month": "2024-12"}</t>
-        </is>
-      </c>
-      <c r="H95" t="inlineStr">
-        <is>
-          <t>sampled values are supported by source text/path</t>
-        </is>
-      </c>
-      <c r="I95" t="inlineStr">
-        <is>
-          <t>CORRECT</t>
-        </is>
-      </c>
-      <c r="J95" t="inlineStr">
-        <is>
-          <t>supported fields: month; unsupported fields: none</t>
-        </is>
-      </c>
-      <c r="K95" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="L95" t="inlineStr">
-        <is>
-          <t>No parser fix required for sampled row.</t>
-        </is>
-      </c>
-      <c r="M95" t="inlineStr">
-        <is>
-          <t>source read method: fitz</t>
-        </is>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" t="inlineStr">
-        <is>
-          <t>VAL-0095</t>
-        </is>
-      </c>
-      <c r="B96" t="inlineStr">
-        <is>
-          <t>Enrico</t>
-        </is>
-      </c>
-      <c r="C96" t="inlineStr">
-        <is>
-          <t>65</t>
-        </is>
-      </c>
-      <c r="D96" t="inlineStr">
-        <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/09_Enrico_Forwarded/Leistungsnachweis Martin Zahariev Februar 2025.pdf</t>
-        </is>
-      </c>
-      <c r="E96" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="F96" t="inlineStr">
-        <is>
-          <t>month</t>
-        </is>
-      </c>
-      <c r="G96" t="inlineStr">
-        <is>
-          <t>{"month": "2025-02"}</t>
-        </is>
-      </c>
-      <c r="H96" t="inlineStr">
-        <is>
-          <t>sampled values are supported by source text/path</t>
-        </is>
-      </c>
-      <c r="I96" t="inlineStr">
-        <is>
-          <t>CORRECT</t>
-        </is>
-      </c>
-      <c r="J96" t="inlineStr">
-        <is>
-          <t>supported fields: month; unsupported fields: none</t>
-        </is>
-      </c>
-      <c r="K96" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="L96" t="inlineStr">
-        <is>
-          <t>No parser fix required for sampled row.</t>
-        </is>
-      </c>
-      <c r="M96" t="inlineStr">
-        <is>
-          <t>source read method: fitz</t>
-        </is>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" t="inlineStr">
-        <is>
-          <t>VAL-0096</t>
-        </is>
-      </c>
-      <c r="B97" t="inlineStr">
-        <is>
-          <t>Enrico</t>
-        </is>
-      </c>
-      <c r="C97" t="inlineStr">
-        <is>
-          <t>75</t>
-        </is>
-      </c>
-      <c r="D97" t="inlineStr">
-        <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/09_Enrico_Forwarded/Martin Zahariev Gutschrift 48 31.01.2025.pdf</t>
-        </is>
-      </c>
-      <c r="E97" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="F97" t="inlineStr">
-        <is>
-          <t>month; document_number; document_type; amount</t>
-        </is>
-      </c>
-      <c r="G97" t="inlineStr">
-        <is>
-          <t>{"month": "2025-01", "document_number": "48-2025", "document_type": "Gutschrift", "amount": "189578.90"}</t>
-        </is>
-      </c>
-      <c r="H97" t="inlineStr">
-        <is>
-          <t>amount: not found</t>
-        </is>
-      </c>
-      <c r="I97" t="inlineStr">
-        <is>
-          <t>PARTIAL</t>
-        </is>
-      </c>
-      <c r="J97" t="inlineStr">
-        <is>
-          <t>supported fields: month, document_number, document_type; unsupported fields: amount</t>
-        </is>
-      </c>
-      <c r="K97" t="inlineStr">
-        <is>
-          <t>Extracted value was not directly found in the readable source text.</t>
-        </is>
-      </c>
-      <c r="L97" t="inlineStr">
-        <is>
-          <t>Add field-specific validation patterns and source text snippets for this document type.</t>
-        </is>
-      </c>
-      <c r="M97" t="inlineStr">
-        <is>
-          <t>source read method: fitz</t>
-        </is>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" t="inlineStr">
-        <is>
-          <t>VAL-0097</t>
-        </is>
-      </c>
-      <c r="B98" t="inlineStr">
-        <is>
-          <t>Enrico</t>
-        </is>
-      </c>
-      <c r="C98" t="inlineStr">
-        <is>
-          <t>77</t>
-        </is>
-      </c>
-      <c r="D98" t="inlineStr">
-        <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/09_Enrico_Forwarded/Martin Zahariev Gutschrift 52 28.02.2025.pdf</t>
-        </is>
-      </c>
-      <c r="E98" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="F98" t="inlineStr">
-        <is>
-          <t>month; document_number; document_type; amount</t>
-        </is>
-      </c>
-      <c r="G98" t="inlineStr">
-        <is>
-          <t>{"month": "2025-02", "document_number": "52-2025", "document_type": "Gutschrift", "amount": "170271.25"}</t>
-        </is>
-      </c>
-      <c r="H98" t="inlineStr">
-        <is>
-          <t>amount: not found</t>
-        </is>
-      </c>
-      <c r="I98" t="inlineStr">
-        <is>
-          <t>PARTIAL</t>
-        </is>
-      </c>
-      <c r="J98" t="inlineStr">
-        <is>
-          <t>supported fields: month, document_number, document_type; unsupported fields: amount</t>
-        </is>
-      </c>
-      <c r="K98" t="inlineStr">
-        <is>
-          <t>Extracted value was not directly found in the readable source text.</t>
-        </is>
-      </c>
-      <c r="L98" t="inlineStr">
-        <is>
-          <t>Add field-specific validation patterns and source text snippets for this document type.</t>
-        </is>
-      </c>
-      <c r="M98" t="inlineStr">
-        <is>
-          <t>source read method: fitz</t>
-        </is>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" t="inlineStr">
-        <is>
-          <t>VAL-0098</t>
-        </is>
-      </c>
-      <c r="B99" t="inlineStr">
-        <is>
-          <t>Enrico</t>
-        </is>
-      </c>
-      <c r="C99" t="inlineStr">
-        <is>
-          <t>90</t>
-        </is>
-      </c>
-      <c r="D99" t="inlineStr">
-        <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/09_Enrico_Forwarded/Rechnung 2764 Zahariev Hermes Kleidung.pdf</t>
-        </is>
-      </c>
-      <c r="E99" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="F99" t="inlineStr">
-        <is>
-          <t>month; document_number; document_type; amount</t>
-        </is>
-      </c>
-      <c r="G99" t="inlineStr">
-        <is>
-          <t>{"month": "2025-04", "document_number": "02764", "document_type": "Rechnung", "amount": "18.45"}</t>
-        </is>
-      </c>
-      <c r="H99" t="inlineStr">
-        <is>
-          <t>sampled values are supported by source text/path</t>
-        </is>
-      </c>
-      <c r="I99" t="inlineStr">
-        <is>
-          <t>CORRECT</t>
-        </is>
-      </c>
-      <c r="J99" t="inlineStr">
-        <is>
-          <t>supported fields: month, document_number, document_type, amount; unsupported fields: none</t>
-        </is>
-      </c>
-      <c r="K99" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="L99" t="inlineStr">
-        <is>
-          <t>No parser fix required for sampled row.</t>
-        </is>
-      </c>
-      <c r="M99" t="inlineStr">
-        <is>
-          <t>source read method: fitz</t>
-        </is>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" t="inlineStr">
-        <is>
-          <t>VAL-0099</t>
-        </is>
-      </c>
-      <c r="B100" t="inlineStr">
-        <is>
-          <t>Enrico</t>
-        </is>
-      </c>
-      <c r="C100" t="inlineStr">
-        <is>
-          <t>92</t>
-        </is>
-      </c>
-      <c r="D100" t="inlineStr">
-        <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/09_Enrico_Forwarded/Rechnung 2767 Zahariev Hermes Bearbeitungsgebuhr.pdf</t>
-        </is>
-      </c>
-      <c r="E100" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="F100" t="inlineStr">
-        <is>
-          <t>month; document_number; document_type; amount</t>
-        </is>
-      </c>
-      <c r="G100" t="inlineStr">
-        <is>
-          <t>{"month": "2025-04", "document_number": "02767", "document_type": "Rechnung", "amount": "50.58"}</t>
-        </is>
-      </c>
-      <c r="H100" t="inlineStr">
-        <is>
-          <t>sampled values are supported by source text/path</t>
-        </is>
-      </c>
-      <c r="I100" t="inlineStr">
-        <is>
-          <t>CORRECT</t>
-        </is>
-      </c>
-      <c r="J100" t="inlineStr">
-        <is>
-          <t>supported fields: month, document_number, document_type, amount; unsupported fields: none</t>
-        </is>
-      </c>
-      <c r="K100" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="L100" t="inlineStr">
-        <is>
-          <t>No parser fix required for sampled row.</t>
-        </is>
-      </c>
-      <c r="M100" t="inlineStr">
-        <is>
-          <t>source read method: fitz</t>
-        </is>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" t="inlineStr">
-        <is>
-          <t>VAL-0100</t>
-        </is>
-      </c>
-      <c r="B101" t="inlineStr">
-        <is>
-          <t>Enrico</t>
-        </is>
-      </c>
-      <c r="C101" t="inlineStr">
-        <is>
-          <t>95</t>
-        </is>
-      </c>
-      <c r="D101" t="inlineStr">
-        <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/09_Enrico_Forwarded/Rechnung 2812 Zahariev Hermes Sendungsverlust.pdf</t>
-        </is>
-      </c>
-      <c r="E101" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="F101" t="inlineStr">
-        <is>
-          <t>month; document_number; document_type; amount</t>
-        </is>
-      </c>
-      <c r="G101" t="inlineStr">
-        <is>
-          <t>{"month": "2025-07", "document_number": "02812", "document_type": "Rechnung", "amount": "1099.78"}</t>
-        </is>
-      </c>
-      <c r="H101" t="inlineStr">
-        <is>
-          <t>amount: not found</t>
-        </is>
-      </c>
-      <c r="I101" t="inlineStr">
-        <is>
-          <t>PARTIAL</t>
-        </is>
-      </c>
-      <c r="J101" t="inlineStr">
-        <is>
-          <t>supported fields: month, document_number, document_type; unsupported fields: amount</t>
-        </is>
-      </c>
-      <c r="K101" t="inlineStr">
-        <is>
-          <t>Extracted value was not directly found in the readable source text.</t>
-        </is>
-      </c>
-      <c r="L101" t="inlineStr">
-        <is>
-          <t>Add field-specific validation patterns and source text snippets for this document type.</t>
-        </is>
-      </c>
-      <c r="M101" t="inlineStr">
         <is>
           <t>source read method: fitz</t>
         </is>

--- a/08_Reports - Доклади - Berichte/Accounting_Cash_Flow/validation_results.xlsx
+++ b/08_Reports - Доклади - Berichte/Accounting_Cash_Flow/validation_results.xlsx
@@ -2584,12 +2584,12 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>month; creditor; tax_type; amount_paid; unpaid_balance</t>
+          <t>month; creditor; tax_type; amount_paid</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>{"month": "2022-07", "creditor": "Finanzamt", "tax_type": "other public liability", "amount_paid": "-300.00", "unpaid_balance": "19.08"}</t>
+          <t>{"month": "2022-07", "creditor": "Finanzamt", "tax_type": "Finanzamt", "amount_paid": "-300.00"}</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -2599,22 +2599,22 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>CORRECT</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>supported fields: month, creditor, amount_paid, unpaid_balance; unsupported fields: tax_type</t>
+          <t>supported fields: month, creditor, tax_type, amount_paid; unsupported fields: none</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>Extracted value was not directly found in the readable source text.</t>
+          <t/>
         </is>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>Add field-specific validation patterns and source text snippets for this document type.</t>
+          <t>No parser fix required for sampled row.</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
@@ -2651,12 +2651,12 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>month; creditor; tax_type; amount_paid; unpaid_balance</t>
+          <t>month; creditor; tax_type; amount_paid</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>{"month": "2022-10", "creditor": "Finanzamt", "tax_type": "other public liability", "amount_paid": "-1200.00", "unpaid_balance": "30.09"}</t>
+          <t>{"month": "2022-10", "creditor": "Finanzamt", "tax_type": "Finanzamt", "amount_paid": "-1200.00"}</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -2666,22 +2666,22 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>CORRECT</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>supported fields: month, creditor, amount_paid, unpaid_balance; unsupported fields: tax_type</t>
+          <t>supported fields: month, creditor, tax_type, amount_paid; unsupported fields: none</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>Extracted value was not directly found in the readable source text.</t>
+          <t/>
         </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>Add field-specific validation patterns and source text snippets for this document type.</t>
+          <t>No parser fix required for sampled row.</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
@@ -2785,12 +2785,12 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>month; creditor; tax_type; amount_paid; unpaid_balance</t>
+          <t>month; creditor; tax_type; amount_paid</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>{"month": "2024-02", "creditor": "Finanzamt", "tax_type": "Umsatzsteuer", "amount_paid": "18516.48", "unpaid_balance": "0.00"}</t>
+          <t>{"month": "2024-02", "creditor": "Finanzamt", "tax_type": "Umsatzsteuer", "amount_paid": "18516.48"}</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -2805,7 +2805,7 @@
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>supported fields: month, creditor, tax_type, amount_paid, unpaid_balance; unsupported fields: none</t>
+          <t>supported fields: month, creditor, tax_type, amount_paid; unsupported fields: none</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>month; creditor; tax_type; amount_paid; unpaid_balance</t>
+          <t>month; creditor; tax_type; amount_paid</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>{"month": "2024-11", "creditor": "Finanzamt", "tax_type": "Umsatzsteuer", "amount_paid": "27948.98", "unpaid_balance": "0.00"}</t>
+          <t>{"month": "2024-11", "creditor": "Finanzamt", "tax_type": "Umsatzsteuer", "amount_paid": "27948.98"}</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -2939,7 +2939,7 @@
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>supported fields: month, creditor, tax_type, amount_paid, unpaid_balance; unsupported fields: none</t>
+          <t>supported fields: month, creditor, tax_type, amount_paid; unsupported fields: none</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
@@ -3058,7 +3058,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>{"month": "2024-02", "creditor": "Hauptzollamt", "tax_type": "other public liability", "amount_paid": "57567.96"}</t>
+          <t>{"month": "2024-02", "creditor": "Hauptzollamt", "tax_type": "Hauptzollamt", "amount_paid": "57567.96"}</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -3068,22 +3068,22 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>CORRECT</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>supported fields: month, creditor, amount_paid; unsupported fields: tax_type</t>
+          <t>supported fields: month, creditor, tax_type, amount_paid; unsupported fields: none</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>Extracted value was not directly found in the readable source text.</t>
+          <t/>
         </is>
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>Add field-specific validation patterns and source text snippets for this document type.</t>
+          <t>No parser fix required for sampled row.</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
@@ -3125,7 +3125,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>{"month": "2024-06", "creditor": "Hauptzollamt", "tax_type": "other public liability", "amount_paid": "54751.98"}</t>
+          <t>{"month": "2024-06", "creditor": "Hauptzollamt", "tax_type": "Hauptzollamt", "amount_paid": "54751.98"}</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -3135,22 +3135,22 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>CORRECT</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>supported fields: month, creditor, amount_paid; unsupported fields: tax_type</t>
+          <t>supported fields: month, creditor, tax_type, amount_paid; unsupported fields: none</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>Extracted value was not directly found in the readable source text.</t>
+          <t/>
         </is>
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>Add field-specific validation patterns and source text snippets for this document type.</t>
+          <t>No parser fix required for sampled row.</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
@@ -3192,7 +3192,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>{"month": "2024-10", "creditor": "Hauptzollamt", "tax_type": "other public liability", "amount_paid": "1568.99"}</t>
+          <t>{"month": "2024-10", "creditor": "Hauptzollamt", "tax_type": "Hauptzollamt", "amount_paid": "1568.99"}</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -3202,22 +3202,22 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>CORRECT</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>supported fields: month, creditor, amount_paid; unsupported fields: tax_type</t>
+          <t>supported fields: month, creditor, tax_type, amount_paid; unsupported fields: none</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>Extracted value was not directly found in the readable source text.</t>
+          <t/>
         </is>
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>Add field-specific validation patterns and source text snippets for this document type.</t>
+          <t>No parser fix required for sampled row.</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
@@ -3259,7 +3259,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>{"month": "2025-02", "creditor": "Finanzamt", "tax_type": "other public liability", "amount_paid": "4654.34"}</t>
+          <t>{"month": "2025-02", "creditor": "Finanzamt", "tax_type": "Finanzamt", "amount_paid": "4654.34"}</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -3269,22 +3269,22 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>CORRECT</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>supported fields: month, creditor; unsupported fields: tax_type, amount_paid</t>
+          <t>supported fields: month, creditor, tax_type, amount_paid; unsupported fields: none</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>Extracted value was not directly found in the readable source text.</t>
+          <t/>
         </is>
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>Add field-specific validation patterns and source text snippets for this document type.</t>
+          <t>No parser fix required for sampled row.</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
@@ -3326,7 +3326,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>{"month": "2025-04", "creditor": "Finanzamt", "tax_type": "other public liability", "amount_paid": "3752.34"}</t>
+          <t>{"month": "2025-04", "creditor": "Finanzamt", "tax_type": "Finanzamt", "amount_paid": "3752.34"}</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -3336,22 +3336,22 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>CORRECT</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>supported fields: month, creditor; unsupported fields: tax_type, amount_paid</t>
+          <t>supported fields: month, creditor, tax_type, amount_paid; unsupported fields: none</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>Extracted value was not directly found in the readable source text.</t>
+          <t/>
         </is>
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>Add field-specific validation patterns and source text snippets for this document type.</t>
+          <t>No parser fix required for sampled row.</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
@@ -3775,12 +3775,12 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>10</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/08_Operating_Costs/45474 - Rechnung 241289_2024 vom 27.12.2024, Aufträge 21_24, 31_24, 32_24, 33_24, 34_24, 35_21, 35_24, 50_24, 98_24, Mandant 42303.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/08_Operating_Costs/43029 - Rechnung 240697_2024 vom 31.07.2024, Aufträge 21_23, 21_24, 31_22, 31_23, 31_24, 33_24, 34_24, Mandant 42303.pdf</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -3795,7 +3795,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>{"month": "2024-12", "category": "accounting fees", "amount_due": "20.00", "unpaid_balance": "20.00"}</t>
+          <t>{"month": "2024-07", "category": "accounting fees", "amount_due": "20.00", "unpaid_balance": "20.00"}</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -3842,12 +3842,12 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>14</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/08_Operating_Costs/46851 - Rechnung 250303_2025 vom 31.03.2025, Aufträge 31_25, 33_25, 34_25, Mandant 42303.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/08_Operating_Costs/45474 - Rechnung 241289_2024 vom 27.12.2024, Aufträge 21_24, 31_24, 32_24, 33_24, 34_24, 35_21, 35_24, 50_24, 98_24, Mandant 42303.pdf</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -3862,7 +3862,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>{"month": "2025-03", "category": "accounting fees", "amount_due": "20.00", "unpaid_balance": "20.00"}</t>
+          <t>{"month": "2024-12", "category": "accounting fees", "amount_due": "20.00", "unpaid_balance": "20.00"}</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -3909,12 +3909,12 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/08_Operating_Costs/6106074_020725.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/08_Operating_Costs/46851 - Rechnung 250303_2025 vom 31.03.2025, Aufträge 31_25, 33_25, 34_25, Mandant 42303.pdf</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -3924,12 +3924,12 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>month; category; amount_due</t>
+          <t>month; category; amount_due; unpaid_balance</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>{"month": "2025-06", "category": "fuel", "amount_due": "5270.35"}</t>
+          <t>{"month": "2025-03", "category": "accounting fees", "amount_due": "20.00", "unpaid_balance": "20.00"}</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -3944,7 +3944,7 @@
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>supported fields: month, category, amount_due; unsupported fields: none</t>
+          <t>supported fields: month, category, amount_due, unpaid_balance; unsupported fields: none</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
@@ -3976,12 +3976,12 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/08_Operating_Costs/6106074_040625.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/08_Operating_Costs/6106074_020725.pdf</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -3996,7 +3996,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>{"month": "2025-05", "category": "fuel", "amount_due": "9949.77"}</t>
+          <t>{"month": "2025-06", "category": "fuel", "amount_due": "5270.35"}</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -4043,12 +4043,12 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/08_Operating_Costs/6106074_050825.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/08_Operating_Costs/6106074_040625.pdf</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -4063,7 +4063,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>{"month": "2025-07", "category": "fuel", "amount_due": "1599.35"}</t>
+          <t>{"month": "2025-05", "category": "fuel", "amount_due": "9949.77"}</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -4110,12 +4110,12 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>19</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/08_Operating_Costs/6106074_061224.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/08_Operating_Costs/6106074_050825.pdf</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -4130,7 +4130,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>{"month": "2024-11", "category": "fuel", "amount_due": "18535.34"}</t>
+          <t>{"month": "2025-07", "category": "fuel", "amount_due": "1599.35"}</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -4177,12 +4177,12 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>20</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/08_Operating_Costs/Ihre Lohnauswertungen.eml</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/08_Operating_Costs/6106074_061224.pdf</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -4192,12 +4192,12 @@
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>month; category</t>
+          <t>month; category; amount_due</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>{"month": "2024-09", "category": "accounting fees"}</t>
+          <t>{"month": "2024-11", "category": "fuel", "amount_due": "18535.34"}</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -4207,27 +4207,27 @@
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>WRONG</t>
+          <t>CORRECT</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>supported fields: category; unsupported fields: month</t>
+          <t>supported fields: month, category, amount_due; unsupported fields: none</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>Month parser selected a nearby date or unrelated filename token.</t>
+          <t/>
         </is>
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>Prefer Leistungszeitraum/document period labels and filename month patterns over first date token.</t>
+          <t>No parser fix required for sampled row.</t>
         </is>
       </c>
       <c r="M63" t="inlineStr">
         <is>
-          <t>source read method: eml</t>
+          <t>source read method: fitz</t>
         </is>
       </c>
     </row>
@@ -4244,12 +4244,12 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>24</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/08_Operating_Costs/Martin Zahariev Transporte 2036 08.01.2025 Scannermiete.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/08_Operating_Costs/CarlundCarla_RG424005125.pdf</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -4264,7 +4264,7 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>{"month": "2025-01", "category": "rent", "amount_due": "675.92"}</t>
+          <t>{"month": "2024-09", "category": "fuel", "amount_due": "214.00"}</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
@@ -4311,12 +4311,12 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>26</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/08_Operating_Costs/Martin Zahariev Transporte 2054 07.02.2025 Scannermiete.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/08_Operating_Costs/Martin Zahariev Transporte 2036 08.01.2025 Scannermiete.pdf</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
@@ -4331,7 +4331,7 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>{"month": "2025-02", "category": "rent", "amount_due": "637.84"}</t>
+          <t>{"month": "2025-01", "category": "rent", "amount_due": "675.92"}</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
@@ -4378,12 +4378,12 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>27</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/08_Operating_Costs/Rechnung 2765 Zahariev Hermes Scannermiete.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/08_Operating_Costs/Martin Zahariev Transporte 2054 07.02.2025 Scannermiete.pdf</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
@@ -4393,12 +4393,12 @@
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>category; amount_due</t>
+          <t>month; category; amount_due</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>{"category": "rent", "amount_due": "637.84"}</t>
+          <t>{"month": "2025-02", "category": "rent", "amount_due": "637.84"}</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
@@ -4413,7 +4413,7 @@
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>supported fields: category, amount_due; unsupported fields: none</t>
+          <t>supported fields: month, category, amount_due; unsupported fields: none</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
@@ -4445,12 +4445,12 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>30</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/08_Operating_Costs/Rechnung 2782 Zahariev Hermes Bearbeitungsgebühr.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/08_Operating_Costs/Rechnung 2777 Zahariev Hermes Unterstützungstouren.pdf</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -4460,12 +4460,12 @@
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>month; category; amount_due</t>
+          <t>category; amount_due</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>{"month": "2025-05", "category": "accounting fees", "amount_due": "35.70"}</t>
+          <t>{"category": "accounting fees", "amount_due": "499.80"}</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
@@ -4480,7 +4480,7 @@
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>supported fields: month, category, amount_due; unsupported fields: none</t>
+          <t>supported fields: category, amount_due; unsupported fields: none</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
@@ -4512,12 +4512,12 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>33</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/08_Operating_Costs/Rechnung 2799 Bearbeitungsgebühr 10.06.2025 Zahariev.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/08_Operating_Costs/Rechnung 2788 Zahariev Hermes Scannermiete.pdf</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
@@ -4527,12 +4527,12 @@
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>month; category; amount_due</t>
+          <t>category; amount_due</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>{"month": "2025-06", "category": "accounting fees", "amount_due": "53.55"}</t>
+          <t>{"category": "rent", "amount_due": "523.60"}</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -4547,7 +4547,7 @@
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>supported fields: month, category, amount_due; unsupported fields: none</t>
+          <t>supported fields: category, amount_due; unsupported fields: none</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
@@ -4584,7 +4584,7 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/08_Operating_Costs/Rechnung 2810 Zahariev TF Touren.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/08_Operating_Costs/Rechnung 2811 Zahariev scannermiete.pdf</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
@@ -4599,7 +4599,7 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>{"category": "accounting fees", "amount_due": "9496.20"}</t>
+          <t>{"category": "rent", "amount_due": "333.20"}</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
@@ -4651,7 +4651,7 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/08_Operating_Costs/Rechnung 2811 Zahariev scannermiete.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/08_Operating_Costs/Rechnung 2813 zahariev bearbeitungsgebühr.pdf</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
@@ -4661,12 +4661,12 @@
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>category; amount_due</t>
+          <t>month; category; amount_due</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>{"category": "rent", "amount_due": "333.20"}</t>
+          <t>{"month": "2025-07", "category": "accounting fees", "amount_due": "47.60"}</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
@@ -4681,7 +4681,7 @@
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>supported fields: category, amount_due; unsupported fields: none</t>
+          <t>supported fields: month, category, amount_due; unsupported fields: none</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
@@ -4713,7 +4713,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>48</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -4728,12 +4728,12 @@
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>month; category; creditor; amount_due</t>
+          <t>month; category; amount_due</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>{"month": "2024-01", "category": "fuel", "creditor": "en-Nr: 2000016306", "amount_due": "2543.30"}</t>
+          <t>{"month": "2024-01", "category": "fuel", "amount_due": "2543.30"}</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
@@ -4743,22 +4743,22 @@
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>CORRECT</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>supported fields: month, category, amount_due; unsupported fields: creditor</t>
+          <t>supported fields: month, category, amount_due; unsupported fields: none</t>
         </is>
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>Extracted value was not directly found in the readable source text.</t>
+          <t/>
         </is>
       </c>
       <c r="L71" t="inlineStr">
         <is>
-          <t>Add field-specific validation patterns and source text snippets for this document type.</t>
+          <t>No parser fix required for sampled row.</t>
         </is>
       </c>
       <c r="M71" t="inlineStr">
